--- a/data/output/sim_gridrnd/REL1/group_520_20/results/REL1_G7_results_summary.xlsx
+++ b/data/output/sim_gridrnd/REL1/group_520_20/results/REL1_G7_results_summary.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CM23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,24 +436,24 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>mu</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>sigma</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>jnd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>pse</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>jnd</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sigma</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>mu</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>n_trials</t>
@@ -466,367 +466,422 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>lat_entropy_100</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_120</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_140</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_180</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_200</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_40</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_60</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>lat_entropy_80</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pse_40</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>jnd_40</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>pse_60</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>jnd_60</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>pse_80</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>jnd_80</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>pse_100</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>jnd_100</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>pse_120</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>jnd_120</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>pse_140</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>jnd_140</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>pse_160</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>jnd_160</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>pse_180</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>jnd_180</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>pse_200</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>jnd_200</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_40</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_60</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_80</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_100</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_120</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_140</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_160</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_180</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>asymmetry_200</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_40</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_60</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_80</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_100</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_120</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_140</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_160</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_180</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_center_200</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_40</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_60</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_80</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_100</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_120</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_140</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_160</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_180</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_spread_200</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_40</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_60</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_80</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_100</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_120</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_140</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_160</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_180</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>stimulus_min_200</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_40</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_60</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_80</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_100</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_120</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_140</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_160</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_180</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>stimulus_max_200</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_40</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_60</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_80</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_100</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_120</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_140</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_160</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_180</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>bimodality_index_200</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>pse_est</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>jnd_est</t>
         </is>
       </c>
     </row>
@@ -840,10 +895,10 @@
         <v>519</v>
       </c>
       <c r="C2" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D2" t="n">
         <v>19</v>
-      </c>
-      <c r="D2" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E2" t="n">
         <v>519</v>
@@ -852,228 +907,261 @@
         <v>200</v>
       </c>
       <c r="G2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H2" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I2" t="n">
-        <v>521.3148107570905</v>
-      </c>
-      <c r="J2" t="n">
-        <v>20.24871780515902</v>
-      </c>
-      <c r="K2" t="n">
-        <v>520.9464348051898</v>
-      </c>
-      <c r="L2" t="n">
-        <v>17.73405307158717</v>
-      </c>
-      <c r="M2" t="n">
-        <v>523.8446390117639</v>
-      </c>
-      <c r="N2" t="n">
-        <v>17.2568547639588</v>
-      </c>
-      <c r="O2" t="n">
-        <v>525.3816348252931</v>
-      </c>
-      <c r="P2" t="n">
-        <v>16.8205270687679</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>522.0420737153062</v>
-      </c>
       <c r="R2" t="n">
-        <v>20.96620079683869</v>
+        <v>521.3099999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>525.089762799447</v>
+        <v>20.25</v>
       </c>
       <c r="T2" t="n">
-        <v>21.17255191125852</v>
+        <v>520.95</v>
       </c>
       <c r="U2" t="n">
-        <v>525.9534119949993</v>
+        <v>17.73</v>
       </c>
       <c r="V2" t="n">
-        <v>20.84125920753941</v>
+        <v>523.84</v>
       </c>
       <c r="W2" t="n">
-        <v>524.1907577003711</v>
+        <v>17.26</v>
       </c>
       <c r="X2" t="n">
-        <v>21.19213990792971</v>
+        <v>525.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>523.1944016897551</v>
+        <v>16.82</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.34527506897172</v>
+        <v>522.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>20.97</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>525.09</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>525.95</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>20.84</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>524.1900000000001</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>21.19</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>523.1900000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>21.35</v>
       </c>
       <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
         <v>498.15</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AT2" t="n">
         <v>497.7166666666666</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AU2" t="n">
         <v>497.375</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AV2" t="n">
         <v>497.47</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AW2" t="n">
         <v>498.1333333333333</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AX2" t="n">
         <v>497.8857142857143</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AY2" t="n">
         <v>497.99375</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AZ2" t="n">
         <v>498.0166666666667</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="BA2" t="n">
         <v>498.335</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="BB2" t="n">
         <v>49.18157683523374</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="BC2" t="n">
         <v>45.00336715797558</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="BD2" t="n">
         <v>43.12463767963738</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="BE2" t="n">
         <v>41.34935428758229</v>
       </c>
-      <c r="AW2" t="n">
+      <c r="BF2" t="n">
         <v>39.2118037783976</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BG2" t="n">
         <v>38.58128445508368</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BH2" t="n">
         <v>38.81679676296719</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BI2" t="n">
         <v>38.59554882222675</v>
       </c>
-      <c r="BA2" t="n">
+      <c r="BJ2" t="n">
         <v>37.8835422710179</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BK2" t="n">
         <v>335</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BL2" t="n">
         <v>335</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BM2" t="n">
         <v>335</v>
       </c>
-      <c r="BE2" t="n">
+      <c r="BN2" t="n">
         <v>335</v>
       </c>
-      <c r="BF2" t="n">
+      <c r="BO2" t="n">
         <v>335</v>
       </c>
-      <c r="BG2" t="n">
+      <c r="BP2" t="n">
         <v>335</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BQ2" t="n">
         <v>335</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BR2" t="n">
         <v>335</v>
       </c>
-      <c r="BJ2" t="n">
+      <c r="BS2" t="n">
         <v>335</v>
       </c>
-      <c r="BK2" t="n">
+      <c r="BT2" t="n">
         <v>637</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BU2" t="n">
         <v>637</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BV2" t="n">
         <v>637</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BW2" t="n">
         <v>637</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BX2" t="n">
         <v>637</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BY2" t="n">
         <v>637</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BZ2" t="n">
         <v>637</v>
       </c>
-      <c r="BR2" t="n">
+      <c r="CA2" t="n">
         <v>637</v>
       </c>
-      <c r="BS2" t="n">
+      <c r="CB2" t="n">
         <v>637</v>
       </c>
-      <c r="BT2" t="n">
+      <c r="CC2" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
+      <c r="CD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE2" t="n">
         <v>0.6538461538461539</v>
       </c>
-      <c r="BW2" t="n">
+      <c r="CF2" t="n">
         <v>0.7666666666666667</v>
       </c>
-      <c r="BX2" t="n">
+      <c r="CG2" t="n">
         <v>0.7105263157894737</v>
       </c>
-      <c r="BY2" t="n">
+      <c r="CH2" t="n">
         <v>0.6818181818181818</v>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CI2" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CJ2" t="n">
         <v>0.7346938775510204</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CK2" t="n">
         <v>0.7090909090909091</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>523.1900000000001</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>21.35</v>
       </c>
     </row>
     <row r="3">
@@ -1086,10 +1174,10 @@
         <v>520</v>
       </c>
       <c r="C3" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D3" t="n">
         <v>18</v>
-      </c>
-      <c r="D3" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E3" t="n">
         <v>520</v>
@@ -1098,228 +1186,261 @@
         <v>200</v>
       </c>
       <c r="G3" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H3" t="inlineStr">
+        <v>80</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J3" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I3" t="n">
-        <v>525.2925152451727</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.053156244738755</v>
-      </c>
-      <c r="K3" t="n">
-        <v>526.5731428612784</v>
-      </c>
-      <c r="L3" t="n">
-        <v>2.36821693098034</v>
-      </c>
-      <c r="M3" t="n">
-        <v>521.705708945135</v>
-      </c>
-      <c r="N3" t="n">
-        <v>16.89972121289746</v>
-      </c>
-      <c r="O3" t="n">
-        <v>521.9323031177222</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15.19940459690668</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>521.129006011374</v>
-      </c>
       <c r="R3" t="n">
-        <v>17.94083584646297</v>
+        <v>525.29</v>
       </c>
       <c r="S3" t="n">
-        <v>518.9821832897288</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
-        <v>19.81844748637391</v>
+        <v>526.5700000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>517.7084404624321</v>
+        <v>2.37</v>
       </c>
       <c r="V3" t="n">
-        <v>20.93709832721246</v>
+        <v>521.71</v>
       </c>
       <c r="W3" t="n">
-        <v>516.6751308603597</v>
+        <v>16.9</v>
       </c>
       <c r="X3" t="n">
-        <v>22.75274187720009</v>
+        <v>521.9299999999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>517.2593435383967</v>
+        <v>15.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.01930851895203</v>
+        <v>521.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>17.94</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>518.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>19.82</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>517.71</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>20.94</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>516.6799999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>517.26</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>22.02</v>
       </c>
       <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>494.45</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AT3" t="n">
         <v>495.4</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AU3" t="n">
         <v>496.45</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AV3" t="n">
         <v>497.16</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AW3" t="n">
         <v>497.55</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AX3" t="n">
         <v>497.5071428571429</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AY3" t="n">
         <v>497.48125</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AZ3" t="n">
         <v>497.5722222222222</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="BA3" t="n">
         <v>497.59</v>
       </c>
-      <c r="AS3" t="n">
+      <c r="BB3" t="n">
         <v>53.29397245467821</v>
       </c>
-      <c r="AT3" t="n">
+      <c r="BC3" t="n">
         <v>47.0039714634129</v>
       </c>
-      <c r="AU3" t="n">
+      <c r="BD3" t="n">
         <v>43.61877462744684</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="BE3" t="n">
         <v>41.39413485024177</v>
       </c>
-      <c r="AW3" t="n">
+      <c r="BF3" t="n">
         <v>39.88563860171561</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="BG3" t="n">
         <v>39.03725261640136</v>
       </c>
-      <c r="AY3" t="n">
+      <c r="BH3" t="n">
         <v>37.92360278820434</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BI3" t="n">
         <v>36.85557858505963</v>
       </c>
-      <c r="BA3" t="n">
+      <c r="BJ3" t="n">
         <v>36.08451052737171</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="BK3" t="n">
         <v>333</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BL3" t="n">
         <v>333</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BM3" t="n">
         <v>333</v>
       </c>
-      <c r="BE3" t="n">
+      <c r="BN3" t="n">
         <v>333</v>
       </c>
-      <c r="BF3" t="n">
+      <c r="BO3" t="n">
         <v>333</v>
       </c>
-      <c r="BG3" t="n">
+      <c r="BP3" t="n">
         <v>333</v>
       </c>
-      <c r="BH3" t="n">
+      <c r="BQ3" t="n">
         <v>333</v>
       </c>
-      <c r="BI3" t="n">
+      <c r="BR3" t="n">
         <v>333</v>
       </c>
-      <c r="BJ3" t="n">
+      <c r="BS3" t="n">
         <v>333</v>
       </c>
-      <c r="BK3" t="n">
+      <c r="BT3" t="n">
         <v>612</v>
       </c>
-      <c r="BL3" t="n">
+      <c r="BU3" t="n">
         <v>612</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BV3" t="n">
         <v>612</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BW3" t="n">
         <v>612</v>
       </c>
-      <c r="BO3" t="n">
+      <c r="BX3" t="n">
         <v>612</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BY3" t="n">
         <v>612</v>
       </c>
-      <c r="BQ3" t="n">
+      <c r="BZ3" t="n">
         <v>612</v>
       </c>
-      <c r="BR3" t="n">
+      <c r="CA3" t="n">
         <v>612</v>
       </c>
-      <c r="BS3" t="n">
+      <c r="CB3" t="n">
         <v>612</v>
       </c>
-      <c r="BT3" t="n">
+      <c r="CC3" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="CD3" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV3" t="n">
+      <c r="CE3" t="n">
         <v>0.8</v>
       </c>
-      <c r="BW3" t="n">
+      <c r="CF3" t="n">
         <v>0.7037037037037037</v>
       </c>
-      <c r="BX3" t="n">
+      <c r="CG3" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="BY3" t="n">
+      <c r="CH3" t="n">
         <v>0.6904761904761905</v>
       </c>
-      <c r="BZ3" t="n">
+      <c r="CI3" t="n">
         <v>0.8809523809523809</v>
       </c>
-      <c r="CA3" t="n">
+      <c r="CJ3" t="n">
         <v>0.9555555555555556</v>
       </c>
-      <c r="CB3" t="n">
+      <c r="CK3" t="n">
         <v>0.8727272727272727</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>517.26</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>22.02</v>
       </c>
     </row>
     <row r="4">
@@ -1332,10 +1453,10 @@
         <v>520</v>
       </c>
       <c r="C4" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D4" t="n">
         <v>18</v>
-      </c>
-      <c r="D4" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E4" t="n">
         <v>520</v>
@@ -1344,736 +1465,835 @@
         <v>200</v>
       </c>
       <c r="G4" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="H4" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I4" t="n">
-        <v>529.5046809360254</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.982309296960983</v>
-      </c>
-      <c r="K4" t="n">
-        <v>519.8380710682856</v>
-      </c>
-      <c r="L4" t="n">
-        <v>16.63868158884982</v>
-      </c>
-      <c r="M4" t="n">
-        <v>517.5562752566196</v>
-      </c>
-      <c r="N4" t="n">
-        <v>18.76897545431136</v>
-      </c>
-      <c r="O4" t="n">
-        <v>517.8095896348483</v>
-      </c>
-      <c r="P4" t="n">
-        <v>18.0307095562649</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>518.7854137217455</v>
-      </c>
       <c r="R4" t="n">
-        <v>16.56886212968533</v>
+        <v>529.5</v>
       </c>
       <c r="S4" t="n">
-        <v>517.1939101737701</v>
+        <v>3.98</v>
       </c>
       <c r="T4" t="n">
-        <v>21.43175282313258</v>
+        <v>519.84</v>
       </c>
       <c r="U4" t="n">
-        <v>519.3596512266458</v>
+        <v>16.64</v>
       </c>
       <c r="V4" t="n">
-        <v>20.90780095302523</v>
+        <v>517.5599999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>519.663594366195</v>
+        <v>18.77</v>
       </c>
       <c r="X4" t="n">
-        <v>20.25264184802239</v>
+        <v>517.8099999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>518.8498314850231</v>
+        <v>18.03</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.19754608623967</v>
+        <v>518.79</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>16.57</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>517.1900000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>21.43</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>519.36</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>20.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>519.66</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>20.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>518.85</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
         <v>501.825</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AT4" t="n">
         <v>500.8666666666667</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AU4" t="n">
         <v>500.0875</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AV4" t="n">
         <v>499.94</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AW4" t="n">
         <v>499.575</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AX4" t="n">
         <v>499.45</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AY4" t="n">
         <v>499.7125</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AZ4" t="n">
         <v>499.8111111111111</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="BA4" t="n">
         <v>499.845</v>
       </c>
-      <c r="AS4" t="n">
+      <c r="BB4" t="n">
         <v>53.12103514616408</v>
       </c>
-      <c r="AT4" t="n">
+      <c r="BC4" t="n">
         <v>46.55300443819091</v>
       </c>
-      <c r="AU4" t="n">
+      <c r="BD4" t="n">
         <v>42.17054474096819</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="BE4" t="n">
         <v>39.33136661749754</v>
       </c>
-      <c r="AW4" t="n">
+      <c r="BF4" t="n">
         <v>37.34359884906649</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="BG4" t="n">
         <v>36.1580508719309</v>
       </c>
-      <c r="AY4" t="n">
+      <c r="BH4" t="n">
         <v>34.98846015116984</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BI4" t="n">
         <v>34.96820601773511</v>
       </c>
-      <c r="BA4" t="n">
+      <c r="BJ4" t="n">
         <v>33.81229029509832</v>
       </c>
-      <c r="BB4" t="n">
+      <c r="BK4" t="n">
         <v>399</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BL4" t="n">
         <v>399</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BM4" t="n">
         <v>399</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BN4" t="n">
         <v>399</v>
       </c>
-      <c r="BF4" t="n">
+      <c r="BO4" t="n">
         <v>399</v>
       </c>
-      <c r="BG4" t="n">
+      <c r="BP4" t="n">
         <v>399</v>
       </c>
-      <c r="BH4" t="n">
+      <c r="BQ4" t="n">
         <v>399</v>
       </c>
-      <c r="BI4" t="n">
+      <c r="BR4" t="n">
         <v>399</v>
       </c>
-      <c r="BJ4" t="n">
+      <c r="BS4" t="n">
         <v>399</v>
       </c>
-      <c r="BK4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>669</v>
-      </c>
       <c r="BT4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC4" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="BU4" t="n">
+      <c r="CD4" t="n">
         <v>0.55</v>
       </c>
-      <c r="BV4" t="n">
+      <c r="CE4" t="n">
         <v>0.6521739130434783</v>
       </c>
-      <c r="BW4" t="n">
+      <c r="CF4" t="n">
         <v>0.7391304347826086</v>
       </c>
-      <c r="BX4" t="n">
+      <c r="CG4" t="n">
         <v>0.76</v>
       </c>
-      <c r="BY4" t="n">
+      <c r="CH4" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BZ4" t="n">
+      <c r="CI4" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="CA4" t="n">
+      <c r="CJ4" t="n">
         <v>0.7173913043478261</v>
       </c>
-      <c r="CB4" t="n">
+      <c r="CK4" t="n">
         <v>0.8043478260869565</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>518.85</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S05_G7_522_19_REL1</t>
+          <t>S04_G7_520_18_REL1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C5" t="n">
-        <v>19</v>
+        <v>26.68643439584878</v>
       </c>
       <c r="D5" t="n">
-        <v>28.16901408450704</v>
+        <v>18</v>
       </c>
       <c r="E5" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F5" t="n">
         <v>200</v>
       </c>
       <c r="G5" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H5" t="inlineStr">
+        <v>78</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I5" t="n">
-        <v>527.1272978775919</v>
-      </c>
-      <c r="J5" t="n">
-        <v>25.76271189549776</v>
-      </c>
-      <c r="K5" t="n">
-        <v>526.5508604291067</v>
-      </c>
-      <c r="L5" t="n">
-        <v>20.97066403189525</v>
-      </c>
-      <c r="M5" t="n">
-        <v>528.0333693192623</v>
-      </c>
-      <c r="N5" t="n">
-        <v>18.06123037184022</v>
-      </c>
-      <c r="O5" t="n">
-        <v>529.1158390126595</v>
-      </c>
-      <c r="P5" t="n">
-        <v>17.1836063154051</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>527.784545308956</v>
-      </c>
       <c r="R5" t="n">
-        <v>20.1470862454208</v>
+        <v>514.27</v>
       </c>
       <c r="S5" t="n">
-        <v>526.9147987582414</v>
+        <v>15.41</v>
       </c>
       <c r="T5" t="n">
-        <v>19.19235031121092</v>
+        <v>515.1</v>
       </c>
       <c r="U5" t="n">
-        <v>525.6764109486372</v>
+        <v>17.53</v>
       </c>
       <c r="V5" t="n">
-        <v>21.58496971274336</v>
+        <v>514.27</v>
       </c>
       <c r="W5" t="n">
-        <v>523.3314499825259</v>
+        <v>19.13</v>
       </c>
       <c r="X5" t="n">
-        <v>20.11961171659162</v>
+        <v>515.86</v>
       </c>
       <c r="Y5" t="n">
-        <v>521.5203338908052</v>
+        <v>21.07</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.95589541803622</v>
+        <v>519.88</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>22.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>520.16</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>22.05</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>520.15</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>23.97</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>517.74</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>24.09</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>516.9299999999999</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>23.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>494.175</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>496.4</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>496.7125</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>496.77</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>497.25</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>497.1357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>497.2</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>497.7277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>497.705</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>59.95743802898853</v>
+        <v>499.65</v>
       </c>
       <c r="AT5" t="n">
-        <v>52.7902137395433</v>
+        <v>499.5166666666667</v>
       </c>
       <c r="AU5" t="n">
-        <v>48.2851410244394</v>
+        <v>499.325</v>
       </c>
       <c r="AV5" t="n">
-        <v>45.96299707373312</v>
+        <v>498.95</v>
       </c>
       <c r="AW5" t="n">
-        <v>44.49779957106493</v>
+        <v>498.9666666666666</v>
       </c>
       <c r="AX5" t="n">
-        <v>43.4194180908374</v>
+        <v>499.1642857142857</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.38628905672211</v>
+        <v>499.40625</v>
       </c>
       <c r="AZ5" t="n">
-        <v>41.35870599678373</v>
+        <v>499.3777777777778</v>
       </c>
       <c r="BA5" t="n">
-        <v>40.36468722782328</v>
+        <v>499.11</v>
       </c>
       <c r="BB5" t="n">
-        <v>335</v>
+        <v>48.80858018832345</v>
       </c>
       <c r="BC5" t="n">
-        <v>335</v>
+        <v>42.48509215660895</v>
       </c>
       <c r="BD5" t="n">
-        <v>335</v>
+        <v>39.23830239702018</v>
       </c>
       <c r="BE5" t="n">
-        <v>335</v>
+        <v>37.36960663426898</v>
       </c>
       <c r="BF5" t="n">
-        <v>335</v>
+        <v>36.95062771982214</v>
       </c>
       <c r="BG5" t="n">
-        <v>335</v>
+        <v>38.27599223576906</v>
       </c>
       <c r="BH5" t="n">
-        <v>335</v>
+        <v>39.90305390490182</v>
       </c>
       <c r="BI5" t="n">
-        <v>335</v>
+        <v>38.33509496757299</v>
       </c>
       <c r="BJ5" t="n">
-        <v>335</v>
+        <v>37.33587952626803</v>
       </c>
       <c r="BK5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BL5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BM5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BN5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BO5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BP5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BQ5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BR5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BS5" t="n">
-        <v>589</v>
+        <v>369</v>
       </c>
       <c r="BT5" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.05263157894736842</v>
+        <v>669</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.6428571428571429</v>
+        <v>669</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.5945945945945946</v>
+        <v>669</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.5531914893617021</v>
+        <v>669</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.5263157894736842</v>
+        <v>669</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.01492537313432836</v>
+        <v>669</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.5194805194805194</v>
+        <v>669</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.7560975609756098</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.8780487804878049</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.9512195121951219</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>516.9299999999999</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>23.36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S06_G7_520_18_REL1</t>
+          <t>S05_G7_522_19_REL1</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D6" t="n">
-        <v>26.68643439584878</v>
+        <v>19</v>
       </c>
       <c r="E6" t="n">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="F6" t="n">
         <v>200</v>
       </c>
       <c r="G6" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H6" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>516.2741129670045</v>
-      </c>
-      <c r="J6" t="n">
-        <v>22.25120056196003</v>
-      </c>
-      <c r="K6" t="n">
-        <v>514.2299063032532</v>
-      </c>
-      <c r="L6" t="n">
-        <v>22.06344221078185</v>
-      </c>
-      <c r="M6" t="n">
-        <v>508.8850929349023</v>
-      </c>
-      <c r="N6" t="n">
-        <v>21.95610673412689</v>
-      </c>
-      <c r="O6" t="n">
-        <v>509.8564881039629</v>
-      </c>
-      <c r="P6" t="n">
-        <v>19.81163092766695</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>512.4925053858489</v>
-      </c>
       <c r="R6" t="n">
-        <v>18.21811584264469</v>
+        <v>527.13</v>
       </c>
       <c r="S6" t="n">
-        <v>509.8906050545713</v>
+        <v>25.76</v>
       </c>
       <c r="T6" t="n">
-        <v>18.4885663729063</v>
+        <v>526.55</v>
       </c>
       <c r="U6" t="n">
-        <v>509.6878542771836</v>
+        <v>20.97</v>
       </c>
       <c r="V6" t="n">
-        <v>18.81215345697165</v>
+        <v>528.03</v>
       </c>
       <c r="W6" t="n">
-        <v>511.7863962491343</v>
+        <v>18.06</v>
       </c>
       <c r="X6" t="n">
-        <v>22.1566859820255</v>
+        <v>529.12</v>
       </c>
       <c r="Y6" t="n">
-        <v>512.9188718224939</v>
+        <v>17.18</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.83685751517583</v>
+        <v>527.78</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>20.15</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>526.91</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>19.19</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>525.6799999999999</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>21.58</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>523.33</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>20.12</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>521.52</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>22.96</v>
       </c>
       <c r="AJ6" t="n">
-        <v>492.4</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>494.3666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>495.2875</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>496.83</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>496.125</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>496.9285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>497.54375</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>497.6277777777778</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>497.55</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>55.23124115932939</v>
+        <v>494.175</v>
       </c>
       <c r="AT6" t="n">
-        <v>48.41245248441309</v>
+        <v>496.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>43.75448369881651</v>
+        <v>496.7125</v>
       </c>
       <c r="AV6" t="n">
-        <v>40.65367265081962</v>
+        <v>496.77</v>
       </c>
       <c r="AW6" t="n">
-        <v>37.92197307191</v>
+        <v>497.25</v>
       </c>
       <c r="AX6" t="n">
-        <v>36.08019695407577</v>
+        <v>497.1357142857143</v>
       </c>
       <c r="AY6" t="n">
-        <v>34.9706746565962</v>
+        <v>497.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>34.22426536108807</v>
+        <v>497.7277777777778</v>
       </c>
       <c r="BA6" t="n">
-        <v>35.30534662058992</v>
+        <v>497.705</v>
       </c>
       <c r="BB6" t="n">
-        <v>326</v>
+        <v>59.95743802898853</v>
       </c>
       <c r="BC6" t="n">
-        <v>326</v>
+        <v>52.7902137395433</v>
       </c>
       <c r="BD6" t="n">
-        <v>326</v>
+        <v>48.2851410244394</v>
       </c>
       <c r="BE6" t="n">
-        <v>326</v>
+        <v>45.96299707373312</v>
       </c>
       <c r="BF6" t="n">
-        <v>326</v>
+        <v>44.49779957106493</v>
       </c>
       <c r="BG6" t="n">
-        <v>326</v>
+        <v>43.4194180908374</v>
       </c>
       <c r="BH6" t="n">
-        <v>326</v>
+        <v>42.38628905672211</v>
       </c>
       <c r="BI6" t="n">
-        <v>326</v>
+        <v>41.35870599678373</v>
       </c>
       <c r="BJ6" t="n">
-        <v>326</v>
+        <v>40.36468722782328</v>
       </c>
       <c r="BK6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BL6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BM6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BN6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BO6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BP6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BQ6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BR6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BS6" t="n">
-        <v>573</v>
+        <v>335</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.1666666666666667</v>
+        <v>589</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.8181818181818182</v>
+        <v>589</v>
       </c>
       <c r="BV6" t="n">
+        <v>589</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>589</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>589</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>589</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>589</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>589</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>589</v>
+      </c>
+      <c r="CC6" t="n">
         <v>1</v>
       </c>
-      <c r="BW6" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>0.8947368421052632</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="BZ6" t="n">
-        <v>0.8928571428571429</v>
-      </c>
-      <c r="CA6" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="CB6" t="n">
-        <v>0.9666666666666667</v>
+      <c r="CD6" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.01492537313432836</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>521.52</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>22.96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S04_G7_520_18_REL1</t>
+          <t>S06_G7_520_18_REL1</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>520</v>
       </c>
       <c r="C7" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D7" t="n">
         <v>18</v>
-      </c>
-      <c r="D7" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E7" t="n">
         <v>520</v>
@@ -2082,244 +2302,277 @@
         <v>200</v>
       </c>
       <c r="G7" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H7" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I7" t="n">
-        <v>514.2718758811811</v>
-      </c>
-      <c r="J7" t="n">
-        <v>15.40587380728711</v>
-      </c>
-      <c r="K7" t="n">
-        <v>515.0986981068135</v>
-      </c>
-      <c r="L7" t="n">
-        <v>17.52948381255376</v>
-      </c>
-      <c r="M7" t="n">
-        <v>514.2718475645339</v>
-      </c>
-      <c r="N7" t="n">
-        <v>19.12871454139811</v>
-      </c>
-      <c r="O7" t="n">
-        <v>515.8635683283516</v>
-      </c>
-      <c r="P7" t="n">
-        <v>21.07353461379114</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>519.8830219395196</v>
-      </c>
       <c r="R7" t="n">
-        <v>22.61776806687227</v>
+        <v>516.27</v>
       </c>
       <c r="S7" t="n">
-        <v>520.1606223479855</v>
+        <v>22.25</v>
       </c>
       <c r="T7" t="n">
-        <v>22.05498919957493</v>
+        <v>514.23</v>
       </c>
       <c r="U7" t="n">
-        <v>520.1467795315066</v>
+        <v>22.06</v>
       </c>
       <c r="V7" t="n">
-        <v>23.97125019742436</v>
+        <v>508.89</v>
       </c>
       <c r="W7" t="n">
-        <v>517.7355816545514</v>
+        <v>21.96</v>
       </c>
       <c r="X7" t="n">
-        <v>24.09188786190141</v>
+        <v>509.86</v>
       </c>
       <c r="Y7" t="n">
-        <v>516.9321779042225</v>
+        <v>19.81</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.35653727597172</v>
+        <v>512.49</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>18.22</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>509.89</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>18.49</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>509.69</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>18.81</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>511.79</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>22.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>512.92</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>22.84</v>
       </c>
       <c r="AJ7" t="n">
-        <v>499.65</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>499.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>499.325</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>498.95</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>498.9666666666666</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>499.1642857142857</v>
+        <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>499.40625</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>499.3777777777778</v>
+        <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>499.11</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>48.80858018832345</v>
+        <v>492.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>42.48509215660895</v>
+        <v>494.3666666666667</v>
       </c>
       <c r="AU7" t="n">
-        <v>39.23830239702018</v>
+        <v>495.2875</v>
       </c>
       <c r="AV7" t="n">
-        <v>37.36960663426898</v>
+        <v>496.83</v>
       </c>
       <c r="AW7" t="n">
-        <v>36.95062771982214</v>
+        <v>496.125</v>
       </c>
       <c r="AX7" t="n">
-        <v>38.27599223576906</v>
+        <v>496.9285714285714</v>
       </c>
       <c r="AY7" t="n">
-        <v>39.90305390490182</v>
+        <v>497.54375</v>
       </c>
       <c r="AZ7" t="n">
-        <v>38.33509496757299</v>
+        <v>497.6277777777778</v>
       </c>
       <c r="BA7" t="n">
-        <v>37.33587952626803</v>
+        <v>497.55</v>
       </c>
       <c r="BB7" t="n">
-        <v>369</v>
+        <v>55.23124115932939</v>
       </c>
       <c r="BC7" t="n">
-        <v>369</v>
+        <v>48.41245248441309</v>
       </c>
       <c r="BD7" t="n">
-        <v>369</v>
+        <v>43.75448369881651</v>
       </c>
       <c r="BE7" t="n">
-        <v>369</v>
+        <v>40.65367265081962</v>
       </c>
       <c r="BF7" t="n">
-        <v>369</v>
+        <v>37.92197307191</v>
       </c>
       <c r="BG7" t="n">
-        <v>369</v>
+        <v>36.08019695407577</v>
       </c>
       <c r="BH7" t="n">
-        <v>369</v>
+        <v>34.9706746565962</v>
       </c>
       <c r="BI7" t="n">
-        <v>369</v>
+        <v>34.22426536108807</v>
       </c>
       <c r="BJ7" t="n">
-        <v>369</v>
+        <v>35.30534662058992</v>
       </c>
       <c r="BK7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BL7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BM7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BN7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BO7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BP7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BQ7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BR7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BS7" t="n">
-        <v>669</v>
+        <v>326</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.125</v>
+        <v>573</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.7222222222222222</v>
+        <v>573</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.7142857142857143</v>
+        <v>573</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.6944444444444444</v>
+        <v>573</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.7560975609756098</v>
+        <v>573</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.8780487804878049</v>
+        <v>573</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.9512195121951219</v>
+        <v>573</v>
       </c>
       <c r="CA7" t="n">
-        <v>0.9512195121951219</v>
+        <v>573</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.9512195121951219</v>
+        <v>573</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>512.92</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>22.84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S08_G7_518_21_REL1</t>
+          <t>S07_G7_518_21_REL1</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>518</v>
       </c>
       <c r="C8" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D8" t="n">
         <v>21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E8" t="n">
         <v>518</v>
@@ -2328,244 +2581,277 @@
         <v>200</v>
       </c>
       <c r="G8" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H8" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>532.322178830503</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4.85676941351449</v>
-      </c>
-      <c r="K8" t="n">
-        <v>536.1836745184212</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13.10396576384131</v>
-      </c>
-      <c r="M8" t="n">
-        <v>528.8972735911484</v>
-      </c>
-      <c r="N8" t="n">
-        <v>20.91857308087343</v>
-      </c>
-      <c r="O8" t="n">
-        <v>527.3693189507371</v>
-      </c>
-      <c r="P8" t="n">
-        <v>20.89910873992777</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>525.6831298756024</v>
-      </c>
       <c r="R8" t="n">
-        <v>22.107226452213</v>
+        <v>517.4</v>
       </c>
       <c r="S8" t="n">
-        <v>522.492977786814</v>
+        <v>20.73</v>
       </c>
       <c r="T8" t="n">
-        <v>24.27902882033237</v>
+        <v>518.4</v>
       </c>
       <c r="U8" t="n">
-        <v>521.1316360198167</v>
+        <v>24.27</v>
       </c>
       <c r="V8" t="n">
-        <v>23.79129440978199</v>
+        <v>516.8200000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>520.2149929585271</v>
+        <v>23.05</v>
       </c>
       <c r="X8" t="n">
-        <v>25.18734279602156</v>
+        <v>517.04</v>
       </c>
       <c r="Y8" t="n">
-        <v>516.7625934583966</v>
+        <v>22.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.43811847401177</v>
+        <v>519.97</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>516.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>22.36</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>517.9</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>28.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>517.53</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>27.61</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>517.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>28.08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>504.95</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>503.65</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>502.2875</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>503.44</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>503.25</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>503.55</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>502.45625</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>501.9111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>500.94</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>53.44808228552264</v>
+        <v>499.875</v>
       </c>
       <c r="AT8" t="n">
-        <v>54.2800838245484</v>
+        <v>500.1333333333333</v>
       </c>
       <c r="AU8" t="n">
-        <v>50.62094273865314</v>
+        <v>499.9375</v>
       </c>
       <c r="AV8" t="n">
-        <v>50.2751071605024</v>
+        <v>498.63</v>
       </c>
       <c r="AW8" t="n">
-        <v>50.88880852735042</v>
+        <v>498.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>51.55500876317866</v>
+        <v>498.5285714285714</v>
       </c>
       <c r="AY8" t="n">
-        <v>50.26390937777821</v>
+        <v>498.68125</v>
       </c>
       <c r="AZ8" t="n">
-        <v>48.76306535903866</v>
+        <v>498.3333333333333</v>
       </c>
       <c r="BA8" t="n">
-        <v>46.93140100188785</v>
+        <v>497.83</v>
       </c>
       <c r="BB8" t="n">
-        <v>379</v>
+        <v>54.95734141131647</v>
       </c>
       <c r="BC8" t="n">
-        <v>379</v>
+        <v>48.30302498003849</v>
       </c>
       <c r="BD8" t="n">
-        <v>379</v>
+        <v>44.97064146473786</v>
       </c>
       <c r="BE8" t="n">
-        <v>379</v>
+        <v>43.16750050674697</v>
       </c>
       <c r="BF8" t="n">
-        <v>379</v>
+        <v>41.12955141987327</v>
       </c>
       <c r="BG8" t="n">
-        <v>379</v>
+        <v>39.77408396307878</v>
       </c>
       <c r="BH8" t="n">
-        <v>379</v>
+        <v>40.47026251999732</v>
       </c>
       <c r="BI8" t="n">
-        <v>379</v>
+        <v>42.97492809120737</v>
       </c>
       <c r="BJ8" t="n">
-        <v>379</v>
+        <v>42.88101094890371</v>
       </c>
       <c r="BK8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BL8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BM8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BN8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BO8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BP8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BQ8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BR8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BS8" t="n">
-        <v>669</v>
+        <v>333</v>
       </c>
       <c r="BT8" t="n">
-        <v>1</v>
+        <v>637</v>
       </c>
       <c r="BU8" t="n">
-        <v>1</v>
+        <v>637</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.6666666666666666</v>
+        <v>637</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.75</v>
+        <v>637</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.9130434782608695</v>
+        <v>637</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.65625</v>
+        <v>637</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.5833333333333334</v>
+        <v>637</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.6052631578947368</v>
+        <v>637</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.9473684210526315</v>
+        <v>637</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CD8" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="CE8" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="CF8" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>0.9565217391304348</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>0.7941176470588235</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>517.67</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>28.08</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S09_G7_518_20_REL1</t>
+          <t>S08_G7_518_21_REL1</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>518</v>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>31.13417346182357</v>
       </c>
       <c r="D9" t="n">
-        <v>29.65159377316531</v>
+        <v>21</v>
       </c>
       <c r="E9" t="n">
         <v>518</v>
@@ -2574,244 +2860,277 @@
         <v>200</v>
       </c>
       <c r="G9" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H9" t="inlineStr">
+        <v>83.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="O9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>522.7665914598523</v>
-      </c>
-      <c r="J9" t="n">
-        <v>30.73659685329504</v>
-      </c>
-      <c r="K9" t="n">
-        <v>518.9983099876606</v>
-      </c>
-      <c r="L9" t="n">
-        <v>25.03994416591839</v>
-      </c>
-      <c r="M9" t="n">
-        <v>512.7184679117855</v>
-      </c>
-      <c r="N9" t="n">
-        <v>26.0280117536684</v>
-      </c>
-      <c r="O9" t="n">
-        <v>511.9667668844327</v>
-      </c>
-      <c r="P9" t="n">
-        <v>29.40467663187637</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>516.7044474419237</v>
-      </c>
       <c r="R9" t="n">
-        <v>27.56723145549929</v>
+        <v>532.3200000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>514.3837361706989</v>
+        <v>4.86</v>
       </c>
       <c r="T9" t="n">
-        <v>25.76990242037822</v>
+        <v>536.1799999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>512.8956146303598</v>
+        <v>13.1</v>
       </c>
       <c r="V9" t="n">
-        <v>25.09161270603931</v>
+        <v>528.9</v>
       </c>
       <c r="W9" t="n">
-        <v>512.4437847589389</v>
+        <v>20.92</v>
       </c>
       <c r="X9" t="n">
-        <v>26.71665702710277</v>
+        <v>527.37</v>
       </c>
       <c r="Y9" t="n">
-        <v>515.4482149152062</v>
+        <v>20.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>26.79484900130634</v>
+        <v>525.6799999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>522.49</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>24.28</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>521.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>23.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>520.21</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>25.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>516.76</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>26.44</v>
       </c>
       <c r="AJ9" t="n">
-        <v>497.45</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>497.8833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>498.65</v>
+        <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>497.92</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>497.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>497.8285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>497.78125</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>497.5555555555555</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>497.55</v>
+        <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>63.48501791761581</v>
+        <v>504.95</v>
       </c>
       <c r="AT9" t="n">
-        <v>55.08481087277044</v>
+        <v>503.65</v>
       </c>
       <c r="AU9" t="n">
-        <v>49.67823970311348</v>
+        <v>502.2875</v>
       </c>
       <c r="AV9" t="n">
-        <v>47.76163313790683</v>
+        <v>503.44</v>
       </c>
       <c r="AW9" t="n">
-        <v>45.67986123251933</v>
+        <v>503.25</v>
       </c>
       <c r="AX9" t="n">
-        <v>44.54162465077595</v>
+        <v>503.55</v>
       </c>
       <c r="AY9" t="n">
-        <v>43.02799551963233</v>
+        <v>502.45625</v>
       </c>
       <c r="AZ9" t="n">
-        <v>41.97131589579592</v>
+        <v>501.9111111111111</v>
       </c>
       <c r="BA9" t="n">
-        <v>41.35139054493815</v>
+        <v>500.94</v>
       </c>
       <c r="BB9" t="n">
-        <v>373</v>
+        <v>53.44808228552264</v>
       </c>
       <c r="BC9" t="n">
-        <v>373</v>
+        <v>54.2800838245484</v>
       </c>
       <c r="BD9" t="n">
-        <v>373</v>
+        <v>50.62094273865314</v>
       </c>
       <c r="BE9" t="n">
-        <v>373</v>
+        <v>50.2751071605024</v>
       </c>
       <c r="BF9" t="n">
-        <v>373</v>
+        <v>50.88880852735042</v>
       </c>
       <c r="BG9" t="n">
-        <v>373</v>
+        <v>51.55500876317866</v>
       </c>
       <c r="BH9" t="n">
-        <v>373</v>
+        <v>50.26390937777821</v>
       </c>
       <c r="BI9" t="n">
-        <v>373</v>
+        <v>48.76306535903866</v>
       </c>
       <c r="BJ9" t="n">
-        <v>373</v>
+        <v>46.93140100188785</v>
       </c>
       <c r="BK9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BL9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BM9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BN9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BO9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BP9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BQ9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BR9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BS9" t="n">
-        <v>669</v>
+        <v>379</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.8888888888888888</v>
+        <v>669</v>
       </c>
       <c r="BU9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE9" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="CF9" t="n">
         <v>0.75</v>
       </c>
-      <c r="BV9" t="n">
-        <v>0.8823529411764706</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY9" t="n">
+      <c r="CG9" t="n">
         <v>0.9130434782608695</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>0.9142857142857143</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.8</v>
+      <c r="CH9" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="CI9" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="CJ9" t="n">
+        <v>0.6052631578947368</v>
+      </c>
+      <c r="CK9" t="n">
+        <v>0.9473684210526315</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>516.76</v>
+      </c>
+      <c r="CM9" t="n">
+        <v>26.44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S07_G7_518_21_REL1</t>
+          <t>S09_G7_518_20_REL1</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>518</v>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D10" t="n">
-        <v>31.13417346182357</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
         <v>518</v>
@@ -2820,474 +3139,540 @@
         <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H10" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I10" t="n">
-        <v>517.3974953773503</v>
-      </c>
-      <c r="J10" t="n">
-        <v>20.72589199581491</v>
-      </c>
-      <c r="K10" t="n">
-        <v>518.3990650231744</v>
-      </c>
-      <c r="L10" t="n">
-        <v>24.27197099013172</v>
-      </c>
-      <c r="M10" t="n">
-        <v>516.823000344897</v>
-      </c>
-      <c r="N10" t="n">
-        <v>23.04785952428294</v>
-      </c>
-      <c r="O10" t="n">
-        <v>517.043350376205</v>
-      </c>
-      <c r="P10" t="n">
-        <v>22.14799979156317</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>519.9665801212388</v>
-      </c>
       <c r="R10" t="n">
-        <v>23.40346978955617</v>
+        <v>522.77</v>
       </c>
       <c r="S10" t="n">
-        <v>516.7584006980782</v>
+        <v>30.74</v>
       </c>
       <c r="T10" t="n">
-        <v>22.36152890793036</v>
+        <v>519</v>
       </c>
       <c r="U10" t="n">
-        <v>517.8987381636258</v>
+        <v>25.04</v>
       </c>
       <c r="V10" t="n">
-        <v>28.67135065921133</v>
+        <v>512.72</v>
       </c>
       <c r="W10" t="n">
-        <v>517.5304867132239</v>
+        <v>26.03</v>
       </c>
       <c r="X10" t="n">
-        <v>27.61494382114518</v>
+        <v>511.97</v>
       </c>
       <c r="Y10" t="n">
-        <v>517.6718668420782</v>
+        <v>29.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>28.07921826105445</v>
+        <v>516.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>27.57</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>514.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>25.77</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>512.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>25.09</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>512.4400000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>26.72</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>515.45</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>26.79</v>
       </c>
       <c r="AJ10" t="n">
-        <v>499.875</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>500.1333333333333</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>499.9375</v>
+        <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>498.63</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
-        <v>498.4</v>
+        <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>498.5285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP10" t="n">
-        <v>498.68125</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>498.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>497.83</v>
+        <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>54.95734141131647</v>
+        <v>497.45</v>
       </c>
       <c r="AT10" t="n">
-        <v>48.30302498003849</v>
+        <v>497.8833333333333</v>
       </c>
       <c r="AU10" t="n">
-        <v>44.97064146473786</v>
+        <v>498.65</v>
       </c>
       <c r="AV10" t="n">
-        <v>43.16750050674697</v>
+        <v>497.92</v>
       </c>
       <c r="AW10" t="n">
-        <v>41.12955141987327</v>
+        <v>497.5166666666667</v>
       </c>
       <c r="AX10" t="n">
-        <v>39.77408396307878</v>
+        <v>497.8285714285714</v>
       </c>
       <c r="AY10" t="n">
-        <v>40.47026251999732</v>
+        <v>497.78125</v>
       </c>
       <c r="AZ10" t="n">
-        <v>42.97492809120737</v>
+        <v>497.5555555555555</v>
       </c>
       <c r="BA10" t="n">
-        <v>42.88101094890371</v>
+        <v>497.55</v>
       </c>
       <c r="BB10" t="n">
-        <v>333</v>
+        <v>63.48501791761581</v>
       </c>
       <c r="BC10" t="n">
-        <v>333</v>
+        <v>55.08481087277044</v>
       </c>
       <c r="BD10" t="n">
-        <v>333</v>
+        <v>49.67823970311348</v>
       </c>
       <c r="BE10" t="n">
-        <v>333</v>
+        <v>47.76163313790683</v>
       </c>
       <c r="BF10" t="n">
-        <v>333</v>
+        <v>45.67986123251933</v>
       </c>
       <c r="BG10" t="n">
-        <v>333</v>
+        <v>44.54162465077595</v>
       </c>
       <c r="BH10" t="n">
-        <v>333</v>
+        <v>43.02799551963233</v>
       </c>
       <c r="BI10" t="n">
-        <v>333</v>
+        <v>41.97131589579592</v>
       </c>
       <c r="BJ10" t="n">
-        <v>333</v>
+        <v>41.35139054493815</v>
       </c>
       <c r="BK10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BL10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BM10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BN10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BO10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BP10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BQ10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BR10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BS10" t="n">
-        <v>637</v>
+        <v>373</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.7272727272727273</v>
+        <v>669</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.04761904761904762</v>
+        <v>669</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.7619047619047619</v>
+        <v>669</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.8095238095238095</v>
+        <v>669</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.9565217391304348</v>
+        <v>669</v>
       </c>
       <c r="BY10" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB10" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC10" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BZ10" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="CB10" t="n">
-        <v>0.7941176470588235</v>
+      <c r="CD10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>515.45</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>26.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S12_G7_522_19_REL1</t>
+          <t>S10_G7_521_22_REL1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D11" t="n">
-        <v>28.16901408450704</v>
+        <v>22</v>
       </c>
       <c r="E11" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F11" t="n">
         <v>200</v>
       </c>
       <c r="G11" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="H11" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>524.4236767984003</v>
-      </c>
-      <c r="J11" t="n">
-        <v>11.34256536409438</v>
-      </c>
-      <c r="K11" t="n">
-        <v>527.3883748598895</v>
-      </c>
-      <c r="L11" t="n">
-        <v>17.50796736921501</v>
-      </c>
-      <c r="M11" t="n">
-        <v>528.8202312021717</v>
-      </c>
-      <c r="N11" t="n">
-        <v>18.07014383556606</v>
-      </c>
-      <c r="O11" t="n">
-        <v>527.7081943747359</v>
-      </c>
-      <c r="P11" t="n">
-        <v>16.19271368831904</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>524.0504351015732</v>
-      </c>
       <c r="R11" t="n">
-        <v>17.37414621106749</v>
+        <v>538.74</v>
       </c>
       <c r="S11" t="n">
-        <v>523.2349401024974</v>
+        <v>5.18</v>
       </c>
       <c r="T11" t="n">
-        <v>17.15024609639369</v>
+        <v>517.65</v>
       </c>
       <c r="U11" t="n">
-        <v>522.7527399143885</v>
+        <v>26.12</v>
       </c>
       <c r="V11" t="n">
-        <v>17.96182616281812</v>
+        <v>517.7</v>
       </c>
       <c r="W11" t="n">
-        <v>523.0957226093345</v>
+        <v>28.47</v>
       </c>
       <c r="X11" t="n">
-        <v>16.61382291966545</v>
+        <v>518.87</v>
       </c>
       <c r="Y11" t="n">
-        <v>522.2949931483175</v>
+        <v>29.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.0404385439021</v>
+        <v>520.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>27.29</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>521.1799999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>25.12</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>519.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>23.31</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>518.8099999999999</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>22.97</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>519.4299999999999</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>23.59</v>
       </c>
       <c r="AJ11" t="n">
-        <v>505.175</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>502.6</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>502.1875</v>
+        <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>502.46</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>501.1166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>501.0285714285714</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>500.64375</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
-        <v>500.2166666666666</v>
+        <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>500.3</v>
+        <v>0</v>
       </c>
       <c r="AS11" t="n">
-        <v>51.33657930754639</v>
+        <v>498.275</v>
       </c>
       <c r="AT11" t="n">
-        <v>50.31043629307939</v>
+        <v>498.5166666666667</v>
       </c>
       <c r="AU11" t="n">
-        <v>52.74350522813211</v>
+        <v>497.2125</v>
       </c>
       <c r="AV11" t="n">
-        <v>48.92226895801134</v>
+        <v>496.68</v>
       </c>
       <c r="AW11" t="n">
-        <v>46.43421571308047</v>
+        <v>497.8083333333333</v>
       </c>
       <c r="AX11" t="n">
-        <v>43.70419117808511</v>
+        <v>497.3785714285714</v>
       </c>
       <c r="AY11" t="n">
-        <v>42.00957433654261</v>
+        <v>497.325</v>
       </c>
       <c r="AZ11" t="n">
-        <v>41.05731427596739</v>
+        <v>497.5111111111111</v>
       </c>
       <c r="BA11" t="n">
-        <v>39.70642265427597</v>
+        <v>497.775</v>
       </c>
       <c r="BB11" t="n">
-        <v>408</v>
+        <v>58.72520221335981</v>
       </c>
       <c r="BC11" t="n">
-        <v>408</v>
+        <v>51.38854984873144</v>
       </c>
       <c r="BD11" t="n">
-        <v>408</v>
+        <v>49.61468879021614</v>
       </c>
       <c r="BE11" t="n">
-        <v>408</v>
+        <v>47.09540954275693</v>
       </c>
       <c r="BF11" t="n">
-        <v>408</v>
+        <v>46.28215923969936</v>
       </c>
       <c r="BG11" t="n">
-        <v>408</v>
+        <v>44.71967733354442</v>
       </c>
       <c r="BH11" t="n">
-        <v>408</v>
+        <v>43.84839649291636</v>
       </c>
       <c r="BI11" t="n">
-        <v>408</v>
+        <v>41.69632129908516</v>
       </c>
       <c r="BJ11" t="n">
-        <v>408</v>
+        <v>40.64953105510567</v>
       </c>
       <c r="BK11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BL11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BM11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BN11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BO11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BP11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BQ11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BR11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BS11" t="n">
-        <v>669</v>
+        <v>360</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.2727272727272727</v>
+        <v>669</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.5625</v>
+        <v>669</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.6875</v>
+        <v>669</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.5625</v>
+        <v>669</v>
       </c>
       <c r="BX11" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.8571428571428571</v>
+        <v>669</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1</v>
+        <v>669</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.896551724137931</v>
+        <v>669</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.8378378378378378</v>
+        <v>669</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>0.7894736842105263</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>0.9130434782608695</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>519.4299999999999</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>23.59</v>
       </c>
     </row>
     <row r="12">
@@ -3300,10 +3685,10 @@
         <v>520</v>
       </c>
       <c r="C12" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D12" t="n">
         <v>22</v>
-      </c>
-      <c r="D12" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E12" t="n">
         <v>520</v>
@@ -3312,474 +3697,540 @@
         <v>200</v>
       </c>
       <c r="G12" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H12" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I12" t="n">
-        <v>523.1840372168792</v>
-      </c>
-      <c r="J12" t="n">
-        <v>14.80970087742259</v>
-      </c>
-      <c r="K12" t="n">
-        <v>516.1300690011182</v>
-      </c>
-      <c r="L12" t="n">
-        <v>26.89296758986149</v>
-      </c>
-      <c r="M12" t="n">
-        <v>508.4158345229283</v>
-      </c>
-      <c r="N12" t="n">
-        <v>29.96930973229707</v>
-      </c>
-      <c r="O12" t="n">
-        <v>513.6577870239603</v>
-      </c>
-      <c r="P12" t="n">
-        <v>27.02762734278975</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>516.4442592041761</v>
-      </c>
       <c r="R12" t="n">
-        <v>24.54903246918871</v>
+        <v>523.1799999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>515.6847649032276</v>
+        <v>14.81</v>
       </c>
       <c r="T12" t="n">
-        <v>22.88895426199014</v>
+        <v>516.13</v>
       </c>
       <c r="U12" t="n">
-        <v>515.6820630018923</v>
+        <v>26.89</v>
       </c>
       <c r="V12" t="n">
-        <v>22.75790961810052</v>
+        <v>508.42</v>
       </c>
       <c r="W12" t="n">
-        <v>514.5873187494428</v>
+        <v>29.97</v>
       </c>
       <c r="X12" t="n">
-        <v>22.37069438484574</v>
+        <v>513.66</v>
       </c>
       <c r="Y12" t="n">
-        <v>513.9466831517724</v>
+        <v>27.03</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.29348222915996</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>24.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>515.6799999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>22.89</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>515.6799999999999</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>22.76</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>514.59</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>22.37</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>513.95</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>21.29</v>
       </c>
       <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
         <v>494</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AT12" t="n">
         <v>494.55</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AU12" t="n">
         <v>494.275</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AV12" t="n">
         <v>495.18</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AW12" t="n">
         <v>495.5416666666667</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AX12" t="n">
         <v>495.8785714285714</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AY12" t="n">
         <v>496.525</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AZ12" t="n">
         <v>496.6722222222222</v>
       </c>
-      <c r="AR12" t="n">
+      <c r="BA12" t="n">
         <v>497.18</v>
       </c>
-      <c r="AS12" t="n">
+      <c r="BB12" t="n">
         <v>57.0753887415583</v>
       </c>
-      <c r="AT12" t="n">
+      <c r="BC12" t="n">
         <v>52.11603240206734</v>
       </c>
-      <c r="AU12" t="n">
+      <c r="BD12" t="n">
         <v>50.97523295679972</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="BE12" t="n">
         <v>47.60386118793307</v>
       </c>
-      <c r="AW12" t="n">
+      <c r="BF12" t="n">
         <v>45.13920982791889</v>
       </c>
-      <c r="AX12" t="n">
+      <c r="BG12" t="n">
         <v>43.22721825377135</v>
       </c>
-      <c r="AY12" t="n">
+      <c r="BH12" t="n">
         <v>42.31842831438805</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BI12" t="n">
         <v>40.79213303179856</v>
       </c>
-      <c r="BA12" t="n">
+      <c r="BJ12" t="n">
         <v>39.95907406334636</v>
       </c>
-      <c r="BB12" t="n">
+      <c r="BK12" t="n">
         <v>338</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BL12" t="n">
         <v>338</v>
       </c>
-      <c r="BD12" t="n">
+      <c r="BM12" t="n">
         <v>338</v>
       </c>
-      <c r="BE12" t="n">
+      <c r="BN12" t="n">
         <v>338</v>
       </c>
-      <c r="BF12" t="n">
+      <c r="BO12" t="n">
         <v>338</v>
       </c>
-      <c r="BG12" t="n">
+      <c r="BP12" t="n">
         <v>338</v>
       </c>
-      <c r="BH12" t="n">
+      <c r="BQ12" t="n">
         <v>338</v>
       </c>
-      <c r="BI12" t="n">
+      <c r="BR12" t="n">
         <v>338</v>
       </c>
-      <c r="BJ12" t="n">
+      <c r="BS12" t="n">
         <v>338</v>
       </c>
-      <c r="BK12" t="n">
+      <c r="BT12" t="n">
         <v>592</v>
       </c>
-      <c r="BL12" t="n">
+      <c r="BU12" t="n">
         <v>592</v>
       </c>
-      <c r="BM12" t="n">
+      <c r="BV12" t="n">
         <v>592</v>
       </c>
-      <c r="BN12" t="n">
+      <c r="BW12" t="n">
         <v>592</v>
       </c>
-      <c r="BO12" t="n">
+      <c r="BX12" t="n">
         <v>592</v>
       </c>
-      <c r="BP12" t="n">
+      <c r="BY12" t="n">
         <v>592</v>
       </c>
-      <c r="BQ12" t="n">
+      <c r="BZ12" t="n">
         <v>592</v>
       </c>
-      <c r="BR12" t="n">
+      <c r="CA12" t="n">
         <v>592</v>
       </c>
-      <c r="BS12" t="n">
+      <c r="CB12" t="n">
         <v>592</v>
       </c>
-      <c r="BT12" t="n">
+      <c r="CC12" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="BU12" t="n">
+      <c r="CD12" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BV12" t="n">
+      <c r="CE12" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW12" t="n">
+      <c r="CF12" t="n">
         <v>1</v>
       </c>
-      <c r="BX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY12" t="n">
+      <c r="CG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH12" t="n">
         <v>0.9473684210526315</v>
       </c>
-      <c r="BZ12" t="n">
+      <c r="CI12" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="CA12" t="n">
+      <c r="CJ12" t="n">
         <v>0.8928571428571429</v>
       </c>
-      <c r="CB12" t="n">
+      <c r="CK12" t="n">
         <v>0.8529411764705882</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>513.95</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>21.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S10_G7_521_22_REL1</t>
+          <t>S12_G7_522_19_REL1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>28.16901408450704</v>
       </c>
       <c r="D13" t="n">
-        <v>32.61675315048184</v>
+        <v>19</v>
       </c>
       <c r="E13" t="n">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F13" t="n">
         <v>200</v>
       </c>
       <c r="G13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H13" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I13" t="n">
-        <v>538.7426471831586</v>
-      </c>
-      <c r="J13" t="n">
-        <v>5.179608901039752</v>
-      </c>
-      <c r="K13" t="n">
-        <v>517.6459273061254</v>
-      </c>
-      <c r="L13" t="n">
-        <v>26.12244899409757</v>
-      </c>
-      <c r="M13" t="n">
-        <v>517.7021762177068</v>
-      </c>
-      <c r="N13" t="n">
-        <v>28.4720469403388</v>
-      </c>
-      <c r="O13" t="n">
-        <v>518.8748972895127</v>
-      </c>
-      <c r="P13" t="n">
-        <v>29.17761884350275</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>520.0812840602875</v>
-      </c>
       <c r="R13" t="n">
-        <v>27.29468475936665</v>
+        <v>524.42</v>
       </c>
       <c r="S13" t="n">
-        <v>521.1830996062802</v>
+        <v>11.34</v>
       </c>
       <c r="T13" t="n">
-        <v>25.12378953328312</v>
+        <v>527.39</v>
       </c>
       <c r="U13" t="n">
-        <v>519.2271826021172</v>
+        <v>17.51</v>
       </c>
       <c r="V13" t="n">
-        <v>23.30973804231473</v>
+        <v>528.8200000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>518.8062434661626</v>
+        <v>18.07</v>
       </c>
       <c r="X13" t="n">
-        <v>22.96790714090302</v>
+        <v>527.71</v>
       </c>
       <c r="Y13" t="n">
-        <v>519.4266390454202</v>
+        <v>16.19</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.58725575353447</v>
+        <v>524.05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>17.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>523.23</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>17.15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>522.75</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>17.96</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>523.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>16.61</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>522.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>17.04</v>
       </c>
       <c r="AJ13" t="n">
-        <v>498.275</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>498.5166666666667</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>497.2125</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>496.68</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>497.8083333333333</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>497.3785714285714</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>497.325</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>497.5111111111111</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>497.775</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>58.72520221335981</v>
+        <v>505.175</v>
       </c>
       <c r="AT13" t="n">
-        <v>51.38854984873144</v>
+        <v>502.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>49.61468879021614</v>
+        <v>502.1875</v>
       </c>
       <c r="AV13" t="n">
-        <v>47.09540954275693</v>
+        <v>502.46</v>
       </c>
       <c r="AW13" t="n">
-        <v>46.28215923969936</v>
+        <v>501.1166666666667</v>
       </c>
       <c r="AX13" t="n">
-        <v>44.71967733354442</v>
+        <v>501.0285714285714</v>
       </c>
       <c r="AY13" t="n">
-        <v>43.84839649291636</v>
+        <v>500.64375</v>
       </c>
       <c r="AZ13" t="n">
-        <v>41.69632129908516</v>
+        <v>500.2166666666666</v>
       </c>
       <c r="BA13" t="n">
-        <v>40.64953105510567</v>
+        <v>500.3</v>
       </c>
       <c r="BB13" t="n">
-        <v>360</v>
+        <v>51.33657930754639</v>
       </c>
       <c r="BC13" t="n">
-        <v>360</v>
+        <v>50.31043629307939</v>
       </c>
       <c r="BD13" t="n">
-        <v>360</v>
+        <v>52.74350522813211</v>
       </c>
       <c r="BE13" t="n">
-        <v>360</v>
+        <v>48.92226895801134</v>
       </c>
       <c r="BF13" t="n">
-        <v>360</v>
+        <v>46.43421571308047</v>
       </c>
       <c r="BG13" t="n">
-        <v>360</v>
+        <v>43.70419117808511</v>
       </c>
       <c r="BH13" t="n">
-        <v>360</v>
+        <v>42.00957433654261</v>
       </c>
       <c r="BI13" t="n">
-        <v>360</v>
+        <v>41.05731427596739</v>
       </c>
       <c r="BJ13" t="n">
-        <v>360</v>
+        <v>39.70642265427597</v>
       </c>
       <c r="BK13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BL13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BM13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BN13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BO13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BP13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BQ13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BR13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BS13" t="n">
-        <v>669</v>
+        <v>408</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.75</v>
+        <v>669</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.625</v>
+        <v>669</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.6470588235294118</v>
+        <v>669</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.7894736842105263</v>
+        <v>669</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.9047619047619048</v>
+        <v>669</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.9130434782608695</v>
+        <v>669</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.8214285714285714</v>
+        <v>669</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.9642857142857143</v>
+        <v>669</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.9090909090909091</v>
+        <v>669</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>0.896551724137931</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>522.29</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>17.04</v>
       </c>
     </row>
     <row r="14">
@@ -3792,10 +4243,10 @@
         <v>522</v>
       </c>
       <c r="C14" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D14" t="n">
         <v>21</v>
-      </c>
-      <c r="D14" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E14" t="n">
         <v>522</v>
@@ -3804,228 +4255,261 @@
         <v>200</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H14" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="N14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I14" t="n">
-        <v>527.5703660833852</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.323042607964083</v>
-      </c>
-      <c r="K14" t="n">
-        <v>530.6725204701794</v>
-      </c>
-      <c r="L14" t="n">
-        <v>15.54361159465345</v>
-      </c>
-      <c r="M14" t="n">
-        <v>528.2945890611437</v>
-      </c>
-      <c r="N14" t="n">
-        <v>14.31128970473922</v>
-      </c>
-      <c r="O14" t="n">
-        <v>526.8898480257983</v>
-      </c>
-      <c r="P14" t="n">
-        <v>14.99400903849077</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>525.7633543567373</v>
-      </c>
       <c r="R14" t="n">
-        <v>14.74732993508514</v>
+        <v>527.5700000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>527.8421442956846</v>
+        <v>4.32</v>
       </c>
       <c r="T14" t="n">
-        <v>14.46131343352151</v>
+        <v>530.67</v>
       </c>
       <c r="U14" t="n">
-        <v>526.0098694342626</v>
+        <v>15.54</v>
       </c>
       <c r="V14" t="n">
-        <v>15.75171490740017</v>
+        <v>528.29</v>
       </c>
       <c r="W14" t="n">
-        <v>525.3745417273693</v>
+        <v>14.31</v>
       </c>
       <c r="X14" t="n">
-        <v>14.78949401889252</v>
+        <v>526.89</v>
       </c>
       <c r="Y14" t="n">
-        <v>524.2185418212688</v>
+        <v>14.99</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.10739872914215</v>
+        <v>525.76</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>14.75</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>527.84</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>14.46</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>526.01</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>15.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>525.37</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>14.79</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>524.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>15.11</v>
       </c>
       <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
         <v>499.4</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AT14" t="n">
         <v>499.6166666666667</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AU14" t="n">
         <v>503.1625</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AV14" t="n">
         <v>501.34</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AW14" t="n">
         <v>501.4833333333333</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AX14" t="n">
         <v>500.8857142857143</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AY14" t="n">
         <v>500.3875</v>
       </c>
-      <c r="AQ14" t="n">
+      <c r="AZ14" t="n">
         <v>500.25</v>
       </c>
-      <c r="AR14" t="n">
+      <c r="BA14" t="n">
         <v>500.445</v>
       </c>
-      <c r="AS14" t="n">
+      <c r="BB14" t="n">
         <v>51.54454384316539</v>
       </c>
-      <c r="AT14" t="n">
+      <c r="BC14" t="n">
         <v>50.4116691738023</v>
       </c>
-      <c r="AU14" t="n">
+      <c r="BD14" t="n">
         <v>48.67608338547792</v>
       </c>
-      <c r="AV14" t="n">
+      <c r="BE14" t="n">
         <v>44.69456790259863</v>
       </c>
-      <c r="AW14" t="n">
+      <c r="BF14" t="n">
         <v>42.02419607268598</v>
       </c>
-      <c r="AX14" t="n">
+      <c r="BG14" t="n">
         <v>40.90321079158976</v>
       </c>
-      <c r="AY14" t="n">
+      <c r="BH14" t="n">
         <v>39.87621275585233</v>
       </c>
-      <c r="AZ14" t="n">
+      <c r="BI14" t="n">
         <v>39.28681924852999</v>
       </c>
-      <c r="BA14" t="n">
+      <c r="BJ14" t="n">
         <v>37.7709805935721</v>
       </c>
-      <c r="BB14" t="n">
+      <c r="BK14" t="n">
         <v>376</v>
       </c>
-      <c r="BC14" t="n">
+      <c r="BL14" t="n">
         <v>376</v>
       </c>
-      <c r="BD14" t="n">
+      <c r="BM14" t="n">
         <v>376</v>
       </c>
-      <c r="BE14" t="n">
+      <c r="BN14" t="n">
         <v>376</v>
       </c>
-      <c r="BF14" t="n">
+      <c r="BO14" t="n">
         <v>376</v>
       </c>
-      <c r="BG14" t="n">
+      <c r="BP14" t="n">
         <v>376</v>
       </c>
-      <c r="BH14" t="n">
+      <c r="BQ14" t="n">
         <v>376</v>
       </c>
-      <c r="BI14" t="n">
+      <c r="BR14" t="n">
         <v>376</v>
       </c>
-      <c r="BJ14" t="n">
+      <c r="BS14" t="n">
         <v>376</v>
       </c>
-      <c r="BK14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>669</v>
-      </c>
       <c r="BT14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB14" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC14" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BU14" t="n">
+      <c r="CD14" t="n">
         <v>1</v>
       </c>
-      <c r="BV14" t="n">
+      <c r="CE14" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="BW14" t="n">
+      <c r="CF14" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BX14" t="n">
+      <c r="CG14" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BY14" t="n">
+      <c r="CH14" t="n">
         <v>0.9545454545454546</v>
       </c>
-      <c r="BZ14" t="n">
+      <c r="CI14" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="CA14" t="n">
+      <c r="CJ14" t="n">
         <v>1</v>
       </c>
-      <c r="CB14" t="n">
+      <c r="CK14" t="n">
         <v>0.8378378378378378</v>
+      </c>
+      <c r="CL14" t="n">
+        <v>524.22</v>
+      </c>
+      <c r="CM14" t="n">
+        <v>15.11</v>
       </c>
     </row>
     <row r="15">
@@ -4038,10 +4522,10 @@
         <v>518</v>
       </c>
       <c r="C15" t="n">
+        <v>32.61675315048184</v>
+      </c>
+      <c r="D15" t="n">
         <v>22</v>
-      </c>
-      <c r="D15" t="n">
-        <v>32.61675315048184</v>
       </c>
       <c r="E15" t="n">
         <v>518</v>
@@ -4050,228 +4534,261 @@
         <v>200</v>
       </c>
       <c r="G15" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="H15" t="inlineStr">
+        <v>77.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I15" t="n">
-        <v>533.5866537712125</v>
-      </c>
-      <c r="J15" t="n">
-        <v>16.91730113865514</v>
-      </c>
-      <c r="K15" t="n">
-        <v>520.8752384183441</v>
-      </c>
-      <c r="L15" t="n">
-        <v>25.96654110844474</v>
-      </c>
-      <c r="M15" t="n">
-        <v>516.6467276987171</v>
-      </c>
-      <c r="N15" t="n">
-        <v>28.05708144422425</v>
-      </c>
-      <c r="O15" t="n">
-        <v>516.0888047900312</v>
-      </c>
-      <c r="P15" t="n">
-        <v>28.02539900863087</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>517.37725707328</v>
-      </c>
       <c r="R15" t="n">
-        <v>26.91144564153781</v>
+        <v>533.59</v>
       </c>
       <c r="S15" t="n">
-        <v>516.6080521470586</v>
+        <v>16.92</v>
       </c>
       <c r="T15" t="n">
-        <v>25.7727860221476</v>
+        <v>520.88</v>
       </c>
       <c r="U15" t="n">
-        <v>514.8175869906507</v>
+        <v>25.97</v>
       </c>
       <c r="V15" t="n">
-        <v>25.20547039693577</v>
+        <v>516.65</v>
       </c>
       <c r="W15" t="n">
-        <v>514.681411790305</v>
+        <v>28.06</v>
       </c>
       <c r="X15" t="n">
-        <v>24.1669287086531</v>
+        <v>516.09</v>
       </c>
       <c r="Y15" t="n">
-        <v>514.0692266954846</v>
+        <v>28.03</v>
       </c>
       <c r="Z15" t="n">
-        <v>25.82677227022178</v>
+        <v>517.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>26.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>516.61</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>25.77</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>25.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>514.6799999999999</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>24.17</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>514.0700000000001</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>25.83</v>
       </c>
       <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
         <v>495.35</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AT15" t="n">
         <v>496.95</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AU15" t="n">
         <v>497.0625</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AV15" t="n">
         <v>497.6</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AW15" t="n">
         <v>498.4583333333333</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AX15" t="n">
         <v>498.7</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AY15" t="n">
         <v>499.075</v>
       </c>
-      <c r="AQ15" t="n">
+      <c r="AZ15" t="n">
         <v>499.0111111111111</v>
       </c>
-      <c r="AR15" t="n">
+      <c r="BA15" t="n">
         <v>499.61</v>
       </c>
-      <c r="AS15" t="n">
+      <c r="BB15" t="n">
         <v>61.03136488724465</v>
       </c>
-      <c r="AT15" t="n">
+      <c r="BC15" t="n">
         <v>53.94979919641344</v>
       </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
         <v>49.96507373906297</v>
       </c>
-      <c r="AV15" t="n">
+      <c r="BE15" t="n">
         <v>47.27472897859913</v>
       </c>
-      <c r="AW15" t="n">
+      <c r="BF15" t="n">
         <v>45.27929913940316</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BG15" t="n">
         <v>43.46767271695796</v>
       </c>
-      <c r="AY15" t="n">
+      <c r="BH15" t="n">
         <v>41.27295573374894</v>
       </c>
-      <c r="AZ15" t="n">
+      <c r="BI15" t="n">
         <v>39.866442152223</v>
       </c>
-      <c r="BA15" t="n">
+      <c r="BJ15" t="n">
         <v>39.61032567399566</v>
       </c>
-      <c r="BB15" t="n">
+      <c r="BK15" t="n">
         <v>326</v>
       </c>
-      <c r="BC15" t="n">
+      <c r="BL15" t="n">
         <v>326</v>
       </c>
-      <c r="BD15" t="n">
+      <c r="BM15" t="n">
         <v>326</v>
       </c>
-      <c r="BE15" t="n">
+      <c r="BN15" t="n">
         <v>326</v>
       </c>
-      <c r="BF15" t="n">
+      <c r="BO15" t="n">
         <v>326</v>
       </c>
-      <c r="BG15" t="n">
+      <c r="BP15" t="n">
         <v>326</v>
       </c>
-      <c r="BH15" t="n">
+      <c r="BQ15" t="n">
         <v>326</v>
       </c>
-      <c r="BI15" t="n">
+      <c r="BR15" t="n">
         <v>326</v>
       </c>
-      <c r="BJ15" t="n">
+      <c r="BS15" t="n">
         <v>326</v>
       </c>
-      <c r="BK15" t="n">
+      <c r="BT15" t="n">
         <v>612</v>
       </c>
-      <c r="BL15" t="n">
+      <c r="BU15" t="n">
         <v>612</v>
       </c>
-      <c r="BM15" t="n">
+      <c r="BV15" t="n">
         <v>612</v>
       </c>
-      <c r="BN15" t="n">
+      <c r="BW15" t="n">
         <v>612</v>
       </c>
-      <c r="BO15" t="n">
+      <c r="BX15" t="n">
         <v>612</v>
       </c>
-      <c r="BP15" t="n">
+      <c r="BY15" t="n">
         <v>612</v>
       </c>
-      <c r="BQ15" t="n">
+      <c r="BZ15" t="n">
         <v>612</v>
       </c>
-      <c r="BR15" t="n">
+      <c r="CA15" t="n">
         <v>612</v>
       </c>
-      <c r="BS15" t="n">
+      <c r="CB15" t="n">
         <v>612</v>
       </c>
-      <c r="BT15" t="n">
+      <c r="CC15" t="n">
         <v>1</v>
       </c>
-      <c r="BU15" t="n">
+      <c r="CD15" t="n">
         <v>0.9090909090909091</v>
       </c>
-      <c r="BV15" t="n">
+      <c r="CE15" t="n">
         <v>0.6842105263157895</v>
       </c>
-      <c r="BW15" t="n">
+      <c r="CF15" t="n">
         <v>0.9</v>
       </c>
-      <c r="BX15" t="n">
+      <c r="CG15" t="n">
         <v>0.95</v>
       </c>
-      <c r="BY15" t="n">
+      <c r="CH15" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BZ15" t="n">
+      <c r="CI15" t="n">
         <v>0.6363636363636364</v>
       </c>
-      <c r="CA15" t="n">
+      <c r="CJ15" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="CB15" t="n">
+      <c r="CK15" t="n">
         <v>0.8</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>514.0700000000001</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>25.83</v>
       </c>
     </row>
     <row r="16">
@@ -4284,10 +4801,10 @@
         <v>518</v>
       </c>
       <c r="C16" t="n">
+        <v>29.65159377316531</v>
+      </c>
+      <c r="D16" t="n">
         <v>20</v>
-      </c>
-      <c r="D16" t="n">
-        <v>29.65159377316531</v>
       </c>
       <c r="E16" t="n">
         <v>518</v>
@@ -4296,228 +4813,261 @@
         <v>200</v>
       </c>
       <c r="G16" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H16" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I16" t="n">
-        <v>513.59264503238</v>
-      </c>
-      <c r="J16" t="n">
-        <v>13.87395881561457</v>
-      </c>
-      <c r="K16" t="n">
-        <v>512.2384508735798</v>
-      </c>
-      <c r="L16" t="n">
-        <v>21.79632469967377</v>
-      </c>
-      <c r="M16" t="n">
-        <v>514.7259810050272</v>
-      </c>
-      <c r="N16" t="n">
-        <v>23.42970481877477</v>
-      </c>
-      <c r="O16" t="n">
-        <v>512.5807031988826</v>
-      </c>
-      <c r="P16" t="n">
-        <v>21.23240155166843</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>512.0959949501635</v>
-      </c>
       <c r="R16" t="n">
-        <v>21.37017817758331</v>
+        <v>513.59</v>
       </c>
       <c r="S16" t="n">
-        <v>513.8778010339418</v>
+        <v>13.87</v>
       </c>
       <c r="T16" t="n">
-        <v>20.91146950331567</v>
+        <v>512.24</v>
       </c>
       <c r="U16" t="n">
-        <v>513.553793258245</v>
+        <v>21.8</v>
       </c>
       <c r="V16" t="n">
-        <v>20.16250842515312</v>
+        <v>514.73</v>
       </c>
       <c r="W16" t="n">
-        <v>514.1919214212963</v>
+        <v>23.43</v>
       </c>
       <c r="X16" t="n">
-        <v>19.54100877173716</v>
+        <v>512.58</v>
       </c>
       <c r="Y16" t="n">
-        <v>514.2731408263264</v>
+        <v>21.23</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.96085437799422</v>
+        <v>512.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>21.37</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>513.88</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>20.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>513.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>20.16</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>514.1900000000001</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>19.54</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>514.27</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>18.96</v>
       </c>
       <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
         <v>504.65</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AT16" t="n">
         <v>503.45</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AU16" t="n">
         <v>502.0375</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AV16" t="n">
         <v>501.68</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AW16" t="n">
         <v>501.9333333333333</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AX16" t="n">
         <v>501.4857142857143</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AY16" t="n">
         <v>501.13125</v>
       </c>
-      <c r="AQ16" t="n">
+      <c r="AZ16" t="n">
         <v>501.7444444444445</v>
       </c>
-      <c r="AR16" t="n">
+      <c r="BA16" t="n">
         <v>501.665</v>
       </c>
-      <c r="AS16" t="n">
+      <c r="BB16" t="n">
         <v>50.41753167302025</v>
       </c>
-      <c r="AT16" t="n">
+      <c r="BC16" t="n">
         <v>44.34351700079731</v>
       </c>
-      <c r="AU16" t="n">
+      <c r="BD16" t="n">
         <v>47.12256459224179</v>
       </c>
-      <c r="AV16" t="n">
+      <c r="BE16" t="n">
         <v>44.23638321562919</v>
       </c>
-      <c r="AW16" t="n">
+      <c r="BF16" t="n">
         <v>42.27562996442382</v>
       </c>
-      <c r="AX16" t="n">
+      <c r="BG16" t="n">
         <v>40.08517462216918</v>
       </c>
-      <c r="AY16" t="n">
+      <c r="BH16" t="n">
         <v>38.42852486679003</v>
       </c>
-      <c r="AZ16" t="n">
+      <c r="BI16" t="n">
         <v>36.91448409232437</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BJ16" t="n">
         <v>35.98753638414278</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BK16" t="n">
         <v>402</v>
       </c>
-      <c r="BC16" t="n">
+      <c r="BL16" t="n">
         <v>402</v>
       </c>
-      <c r="BD16" t="n">
+      <c r="BM16" t="n">
         <v>402</v>
       </c>
-      <c r="BE16" t="n">
+      <c r="BN16" t="n">
         <v>402</v>
       </c>
-      <c r="BF16" t="n">
+      <c r="BO16" t="n">
         <v>402</v>
       </c>
-      <c r="BG16" t="n">
+      <c r="BP16" t="n">
         <v>402</v>
       </c>
-      <c r="BH16" t="n">
+      <c r="BQ16" t="n">
         <v>402</v>
       </c>
-      <c r="BI16" t="n">
+      <c r="BR16" t="n">
         <v>402</v>
       </c>
-      <c r="BJ16" t="n">
+      <c r="BS16" t="n">
         <v>402</v>
       </c>
-      <c r="BK16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>669</v>
-      </c>
       <c r="BT16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC16" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU16" t="n">
+      <c r="CD16" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BV16" t="n">
+      <c r="CE16" t="n">
         <v>0.9285714285714286</v>
       </c>
-      <c r="BW16" t="n">
+      <c r="CF16" t="n">
         <v>0.8888888888888888</v>
       </c>
-      <c r="BX16" t="n">
+      <c r="CG16" t="n">
         <v>0.85</v>
       </c>
-      <c r="BY16" t="n">
+      <c r="CH16" t="n">
         <v>0.9523809523809523</v>
       </c>
-      <c r="BZ16" t="n">
+      <c r="CI16" t="n">
         <v>0.84</v>
       </c>
-      <c r="CA16" t="n">
+      <c r="CJ16" t="n">
         <v>0.6</v>
       </c>
-      <c r="CB16" t="n">
+      <c r="CK16" t="n">
         <v>0.6</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>514.27</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>18.96</v>
       </c>
     </row>
     <row r="17">
@@ -4530,10 +5080,10 @@
         <v>520</v>
       </c>
       <c r="C17" t="n">
+        <v>31.13417346182357</v>
+      </c>
+      <c r="D17" t="n">
         <v>21</v>
-      </c>
-      <c r="D17" t="n">
-        <v>31.13417346182357</v>
       </c>
       <c r="E17" t="n">
         <v>520</v>
@@ -4542,228 +5092,261 @@
         <v>200</v>
       </c>
       <c r="G17" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H17" t="inlineStr">
+        <v>80.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I17" t="n">
-        <v>512.3524420579989</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20.35386129661717</v>
-      </c>
-      <c r="K17" t="n">
-        <v>512.3313234484164</v>
-      </c>
-      <c r="L17" t="n">
-        <v>16.59064548733364</v>
-      </c>
-      <c r="M17" t="n">
-        <v>514.8248168597657</v>
-      </c>
-      <c r="N17" t="n">
-        <v>25.03045279803158</v>
-      </c>
-      <c r="O17" t="n">
-        <v>515.5363893639008</v>
-      </c>
-      <c r="P17" t="n">
-        <v>25.46208397283082</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>517.2024425282239</v>
-      </c>
       <c r="R17" t="n">
-        <v>25.89096515623419</v>
+        <v>512.35</v>
       </c>
       <c r="S17" t="n">
-        <v>514.4499606499343</v>
+        <v>20.35</v>
       </c>
       <c r="T17" t="n">
-        <v>24.8696229229876</v>
+        <v>512.33</v>
       </c>
       <c r="U17" t="n">
-        <v>514.9374321978603</v>
+        <v>16.59</v>
       </c>
       <c r="V17" t="n">
-        <v>24.45956681653872</v>
+        <v>514.8200000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>516.5204201507852</v>
+        <v>25.03</v>
       </c>
       <c r="X17" t="n">
-        <v>23.95256126453899</v>
+        <v>515.54</v>
       </c>
       <c r="Y17" t="n">
-        <v>516.1478594953963</v>
+        <v>25.46</v>
       </c>
       <c r="Z17" t="n">
-        <v>24.2628377884594</v>
+        <v>517.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>25.89</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>514.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>24.87</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>514.9400000000001</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>24.46</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>516.52</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>516.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>24.26</v>
       </c>
       <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
         <v>498.975</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AT17" t="n">
         <v>498.8166666666667</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AU17" t="n">
         <v>499.1875</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AV17" t="n">
         <v>499.06</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AW17" t="n">
         <v>499.2916666666667</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AX17" t="n">
         <v>499.3857142857143</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AY17" t="n">
         <v>499.4875</v>
       </c>
-      <c r="AQ17" t="n">
+      <c r="AZ17" t="n">
         <v>499.2833333333334</v>
       </c>
-      <c r="AR17" t="n">
+      <c r="BA17" t="n">
         <v>499.385</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="BB17" t="n">
         <v>47.50236178338925</v>
       </c>
-      <c r="AT17" t="n">
+      <c r="BC17" t="n">
         <v>43.52183040983251</v>
       </c>
-      <c r="AU17" t="n">
+      <c r="BD17" t="n">
         <v>44.81269177085885</v>
       </c>
-      <c r="AV17" t="n">
+      <c r="BE17" t="n">
         <v>49.87300271690085</v>
       </c>
-      <c r="AW17" t="n">
+      <c r="BF17" t="n">
         <v>50.81771276391289</v>
       </c>
-      <c r="AX17" t="n">
+      <c r="BG17" t="n">
         <v>49.16787361599408</v>
       </c>
-      <c r="AY17" t="n">
+      <c r="BH17" t="n">
         <v>46.98669858321608</v>
       </c>
-      <c r="AZ17" t="n">
+      <c r="BI17" t="n">
         <v>45.30480413574016</v>
       </c>
-      <c r="BA17" t="n">
+      <c r="BJ17" t="n">
         <v>43.48490283995125</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="BK17" t="n">
         <v>362</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BL17" t="n">
         <v>362</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BM17" t="n">
         <v>362</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BN17" t="n">
         <v>362</v>
       </c>
-      <c r="BF17" t="n">
+      <c r="BO17" t="n">
         <v>362</v>
       </c>
-      <c r="BG17" t="n">
+      <c r="BP17" t="n">
         <v>362</v>
       </c>
-      <c r="BH17" t="n">
+      <c r="BQ17" t="n">
         <v>362</v>
       </c>
-      <c r="BI17" t="n">
+      <c r="BR17" t="n">
         <v>362</v>
       </c>
-      <c r="BJ17" t="n">
+      <c r="BS17" t="n">
         <v>362</v>
       </c>
-      <c r="BK17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR17" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS17" t="n">
-        <v>669</v>
-      </c>
       <c r="BT17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY17" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB17" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC17" t="n">
         <v>0.9</v>
       </c>
-      <c r="BU17" t="n">
+      <c r="CD17" t="n">
         <v>0.7333333333333333</v>
       </c>
-      <c r="BV17" t="n">
+      <c r="CE17" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BW17" t="n">
+      <c r="CF17" t="n">
         <v>0.6470588235294118</v>
       </c>
-      <c r="BX17" t="n">
+      <c r="CG17" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" t="n">
+      <c r="CH17" t="n">
         <v>0.8947368421052632</v>
       </c>
-      <c r="BZ17" t="n">
+      <c r="CI17" t="n">
         <v>0.8095238095238095</v>
       </c>
-      <c r="CA17" t="n">
+      <c r="CJ17" t="n">
         <v>0.8076923076923077</v>
       </c>
-      <c r="CB17" t="n">
+      <c r="CK17" t="n">
         <v>0.9655172413793104</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>516.15</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>24.26</v>
       </c>
     </row>
     <row r="18">
@@ -4776,10 +5359,10 @@
         <v>521</v>
       </c>
       <c r="C18" t="n">
+        <v>28.16901408450704</v>
+      </c>
+      <c r="D18" t="n">
         <v>19</v>
-      </c>
-      <c r="D18" t="n">
-        <v>28.16901408450704</v>
       </c>
       <c r="E18" t="n">
         <v>521</v>
@@ -4788,228 +5371,261 @@
         <v>200</v>
       </c>
       <c r="G18" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H18" t="inlineStr">
+        <v>79.5</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I18" t="n">
-        <v>526.7797795421632</v>
-      </c>
-      <c r="J18" t="n">
-        <v>31.0040781129879</v>
-      </c>
-      <c r="K18" t="n">
-        <v>523.0669893607836</v>
-      </c>
-      <c r="L18" t="n">
-        <v>25.5870390856041</v>
-      </c>
-      <c r="M18" t="n">
-        <v>526.5233234834109</v>
-      </c>
-      <c r="N18" t="n">
-        <v>22.45809540667113</v>
-      </c>
-      <c r="O18" t="n">
-        <v>524.0618493821064</v>
-      </c>
-      <c r="P18" t="n">
-        <v>22.06505448762136</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>522.1177209005562</v>
-      </c>
       <c r="R18" t="n">
-        <v>20.55500241904775</v>
+        <v>526.78</v>
       </c>
       <c r="S18" t="n">
-        <v>521.9948493816762</v>
+        <v>31</v>
       </c>
       <c r="T18" t="n">
-        <v>19.72484309721522</v>
+        <v>523.0700000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>520.3297713475239</v>
+        <v>25.59</v>
       </c>
       <c r="V18" t="n">
-        <v>23.50173107964977</v>
+        <v>526.52</v>
       </c>
       <c r="W18" t="n">
-        <v>521.6094266131979</v>
+        <v>22.46</v>
       </c>
       <c r="X18" t="n">
-        <v>22.76801795406605</v>
+        <v>524.0599999999999</v>
       </c>
       <c r="Y18" t="n">
-        <v>520.8592549250822</v>
+        <v>22.07</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.15340021598205</v>
+        <v>522.12</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>20.56</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>521.99</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>19.72</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>520.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>521.61</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>22.77</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>520.86</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>23.15</v>
       </c>
       <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
         <v>498.225</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AT18" t="n">
         <v>498.8666666666667</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AU18" t="n">
         <v>499.05</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AV18" t="n">
         <v>499.25</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AW18" t="n">
         <v>498.8916666666667</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AX18" t="n">
         <v>498.6428571428572</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AY18" t="n">
         <v>498.73125</v>
       </c>
-      <c r="AQ18" t="n">
+      <c r="AZ18" t="n">
         <v>499</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BA18" t="n">
         <v>498.96</v>
       </c>
-      <c r="AS18" t="n">
+      <c r="BB18" t="n">
         <v>59.18677533875283</v>
       </c>
-      <c r="AT18" t="n">
+      <c r="BC18" t="n">
         <v>56.87162932624862</v>
       </c>
-      <c r="AU18" t="n">
+      <c r="BD18" t="n">
         <v>52.15671097759137</v>
       </c>
-      <c r="AV18" t="n">
+      <c r="BE18" t="n">
         <v>49.34174196357482</v>
       </c>
-      <c r="AW18" t="n">
+      <c r="BF18" t="n">
         <v>46.50157628750043</v>
       </c>
-      <c r="AX18" t="n">
+      <c r="BG18" t="n">
         <v>44.44676935529115</v>
       </c>
-      <c r="AY18" t="n">
+      <c r="BH18" t="n">
         <v>42.81672013872034</v>
       </c>
-      <c r="AZ18" t="n">
+      <c r="BI18" t="n">
         <v>42.29538981969548</v>
       </c>
-      <c r="BA18" t="n">
+      <c r="BJ18" t="n">
         <v>41.68726903983998</v>
       </c>
-      <c r="BB18" t="n">
+      <c r="BK18" t="n">
         <v>317</v>
       </c>
-      <c r="BC18" t="n">
+      <c r="BL18" t="n">
         <v>317</v>
       </c>
-      <c r="BD18" t="n">
+      <c r="BM18" t="n">
         <v>317</v>
       </c>
-      <c r="BE18" t="n">
+      <c r="BN18" t="n">
         <v>317</v>
       </c>
-      <c r="BF18" t="n">
+      <c r="BO18" t="n">
         <v>317</v>
       </c>
-      <c r="BG18" t="n">
+      <c r="BP18" t="n">
         <v>317</v>
       </c>
-      <c r="BH18" t="n">
+      <c r="BQ18" t="n">
         <v>317</v>
       </c>
-      <c r="BI18" t="n">
+      <c r="BR18" t="n">
         <v>317</v>
       </c>
-      <c r="BJ18" t="n">
+      <c r="BS18" t="n">
         <v>317</v>
       </c>
-      <c r="BK18" t="n">
+      <c r="BT18" t="n">
         <v>640</v>
       </c>
-      <c r="BL18" t="n">
+      <c r="BU18" t="n">
         <v>640</v>
       </c>
-      <c r="BM18" t="n">
+      <c r="BV18" t="n">
         <v>640</v>
       </c>
-      <c r="BN18" t="n">
+      <c r="BW18" t="n">
         <v>640</v>
       </c>
-      <c r="BO18" t="n">
+      <c r="BX18" t="n">
         <v>640</v>
       </c>
-      <c r="BP18" t="n">
+      <c r="BY18" t="n">
         <v>640</v>
       </c>
-      <c r="BQ18" t="n">
+      <c r="BZ18" t="n">
         <v>640</v>
       </c>
-      <c r="BR18" t="n">
+      <c r="CA18" t="n">
         <v>640</v>
       </c>
-      <c r="BS18" t="n">
+      <c r="CB18" t="n">
         <v>640</v>
       </c>
-      <c r="BT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU18" t="n">
+      <c r="CC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD18" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="BV18" t="n">
+      <c r="CE18" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="BW18" t="n">
+      <c r="CF18" t="n">
         <v>0.7727272727272727</v>
       </c>
-      <c r="BX18" t="n">
+      <c r="CG18" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="BY18" t="n">
+      <c r="CH18" t="n">
         <v>0.84375</v>
       </c>
-      <c r="BZ18" t="n">
+      <c r="CI18" t="n">
         <v>0.9411764705882353</v>
       </c>
-      <c r="CA18" t="n">
+      <c r="CJ18" t="n">
         <v>0.8717948717948718</v>
       </c>
-      <c r="CB18" t="n">
+      <c r="CK18" t="n">
         <v>0.9285714285714286</v>
+      </c>
+      <c r="CL18" t="n">
+        <v>520.86</v>
+      </c>
+      <c r="CM18" t="n">
+        <v>23.15</v>
       </c>
     </row>
     <row r="19">
@@ -5022,10 +5638,10 @@
         <v>519</v>
       </c>
       <c r="C19" t="n">
+        <v>26.68643439584878</v>
+      </c>
+      <c r="D19" t="n">
         <v>18</v>
-      </c>
-      <c r="D19" t="n">
-        <v>26.68643439584878</v>
       </c>
       <c r="E19" t="n">
         <v>519</v>
@@ -5034,720 +5650,819 @@
         <v>200</v>
       </c>
       <c r="G19" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H19" t="inlineStr">
+        <v>78.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I19" t="n">
-        <v>507.217985127856</v>
-      </c>
-      <c r="J19" t="n">
-        <v>25.06903058192835</v>
-      </c>
-      <c r="K19" t="n">
-        <v>522.6950757291287</v>
-      </c>
-      <c r="L19" t="n">
-        <v>28.73639614459616</v>
-      </c>
-      <c r="M19" t="n">
-        <v>521.2145399421116</v>
-      </c>
-      <c r="N19" t="n">
-        <v>24.28955738668067</v>
-      </c>
-      <c r="O19" t="n">
-        <v>522.5069640017927</v>
-      </c>
-      <c r="P19" t="n">
-        <v>22.21366106974868</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>521.8526241926598</v>
-      </c>
       <c r="R19" t="n">
-        <v>22.86026687566658</v>
+        <v>507.22</v>
       </c>
       <c r="S19" t="n">
-        <v>521.7882617970823</v>
+        <v>25.07</v>
       </c>
       <c r="T19" t="n">
-        <v>21.8436826602525</v>
+        <v>522.7</v>
       </c>
       <c r="U19" t="n">
-        <v>519.6853811061887</v>
+        <v>28.74</v>
       </c>
       <c r="V19" t="n">
-        <v>21.3634492042686</v>
+        <v>521.21</v>
       </c>
       <c r="W19" t="n">
-        <v>521.9251557129595</v>
+        <v>24.29</v>
       </c>
       <c r="X19" t="n">
-        <v>20.58169577671316</v>
+        <v>522.51</v>
       </c>
       <c r="Y19" t="n">
-        <v>522.7252674771773</v>
+        <v>22.21</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.02953114678818</v>
+        <v>521.85</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>22.86</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>521.79</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>21.84</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>519.6900000000001</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>21.36</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>521.9299999999999</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>20.58</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>522.73</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>20.03</v>
       </c>
       <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
         <v>501.8</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AT19" t="n">
         <v>501.3833333333333</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AU19" t="n">
         <v>500.0625</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AV19" t="n">
         <v>499.6</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AW19" t="n">
         <v>499.6333333333333</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AX19" t="n">
         <v>499.0285714285714</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AY19" t="n">
         <v>499.31875</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AZ19" t="n">
         <v>499.3166666666667</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="BA19" t="n">
         <v>499.235</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BB19" t="n">
         <v>54.01212826764004</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BC19" t="n">
         <v>47.74867944654479</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="BD19" t="n">
         <v>48.93294998004923</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BE19" t="n">
         <v>46.53514800664118</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BF19" t="n">
         <v>44.27225115376699</v>
       </c>
-      <c r="AX19" t="n">
+      <c r="BG19" t="n">
         <v>42.76613193657251</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="BH19" t="n">
         <v>41.21352506686974</v>
       </c>
-      <c r="AZ19" t="n">
+      <c r="BI19" t="n">
         <v>39.75459092985363</v>
       </c>
-      <c r="BA19" t="n">
+      <c r="BJ19" t="n">
         <v>38.93956567554394</v>
       </c>
-      <c r="BB19" t="n">
+      <c r="BK19" t="n">
         <v>362</v>
       </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
         <v>362</v>
       </c>
-      <c r="BD19" t="n">
+      <c r="BM19" t="n">
         <v>362</v>
       </c>
-      <c r="BE19" t="n">
+      <c r="BN19" t="n">
         <v>362</v>
       </c>
-      <c r="BF19" t="n">
+      <c r="BO19" t="n">
         <v>362</v>
       </c>
-      <c r="BG19" t="n">
+      <c r="BP19" t="n">
         <v>362</v>
       </c>
-      <c r="BH19" t="n">
+      <c r="BQ19" t="n">
         <v>362</v>
       </c>
-      <c r="BI19" t="n">
+      <c r="BR19" t="n">
         <v>362</v>
       </c>
-      <c r="BJ19" t="n">
+      <c r="BS19" t="n">
         <v>362</v>
       </c>
-      <c r="BK19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BQ19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BR19" t="n">
-        <v>669</v>
-      </c>
-      <c r="BS19" t="n">
-        <v>669</v>
-      </c>
       <c r="BT19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BU19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BV19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BW19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BX19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BY19" t="n">
+        <v>669</v>
+      </c>
+      <c r="BZ19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CA19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CB19" t="n">
+        <v>669</v>
+      </c>
+      <c r="CC19" t="n">
         <v>0.8</v>
       </c>
-      <c r="BU19" t="n">
+      <c r="CD19" t="n">
         <v>0.8125</v>
       </c>
-      <c r="BV19" t="n">
+      <c r="CE19" t="n">
         <v>0.7368421052631579</v>
       </c>
-      <c r="BW19" t="n">
+      <c r="CF19" t="n">
         <v>0.9047619047619048</v>
       </c>
-      <c r="BX19" t="n">
+      <c r="CG19" t="n">
         <v>0.88</v>
       </c>
-      <c r="BY19" t="n">
+      <c r="CH19" t="n">
         <v>0.84375</v>
       </c>
-      <c r="BZ19" t="n">
+      <c r="CI19" t="n">
         <v>0.7631578947368421</v>
       </c>
-      <c r="CA19" t="n">
+      <c r="CJ19" t="n">
         <v>0.7173913043478261</v>
       </c>
-      <c r="CB19" t="n">
+      <c r="CK19" t="n">
         <v>0.75</v>
+      </c>
+      <c r="CL19" t="n">
+        <v>522.73</v>
+      </c>
+      <c r="CM19" t="n">
+        <v>20.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S20_G7_521_20_REL1</t>
+          <t>S19_G7_518_22_REL1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>32.61675315048184</v>
       </c>
       <c r="D20" t="n">
-        <v>29.65159377316531</v>
+        <v>22</v>
       </c>
       <c r="E20" t="n">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F20" t="n">
         <v>200</v>
       </c>
       <c r="G20" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="H20" t="inlineStr">
+        <v>76.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I20" t="n">
-        <v>530.7506902941562</v>
-      </c>
-      <c r="J20" t="n">
-        <v>4.482657041186281</v>
-      </c>
-      <c r="K20" t="n">
-        <v>530.1229318074146</v>
-      </c>
-      <c r="L20" t="n">
-        <v>4.626771372175425</v>
-      </c>
-      <c r="M20" t="n">
-        <v>527.7564071344343</v>
-      </c>
-      <c r="N20" t="n">
-        <v>5.536905546460922</v>
-      </c>
-      <c r="O20" t="n">
-        <v>526.3860426408721</v>
-      </c>
-      <c r="P20" t="n">
-        <v>6.170387140611512</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>526.3788340829637</v>
-      </c>
       <c r="R20" t="n">
-        <v>6.10831759888069</v>
+        <v>514.12</v>
       </c>
       <c r="S20" t="n">
-        <v>525.1118529438993</v>
+        <v>19.07</v>
       </c>
       <c r="T20" t="n">
-        <v>14.8153524913314</v>
+        <v>511.98</v>
       </c>
       <c r="U20" t="n">
-        <v>522.9056933927891</v>
+        <v>27.92</v>
       </c>
       <c r="V20" t="n">
-        <v>19.09870623286035</v>
+        <v>515.15</v>
       </c>
       <c r="W20" t="n">
-        <v>520.4351675710056</v>
+        <v>27.24</v>
       </c>
       <c r="X20" t="n">
-        <v>20.00767255475587</v>
+        <v>516.15</v>
       </c>
       <c r="Y20" t="n">
-        <v>517.9545825194006</v>
+        <v>25.72</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.36154328083722</v>
+        <v>515.6799999999999</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>27.86</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>513.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>26.98</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>513.2</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>25.61</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>514.86</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>24.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>515.37</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>25.28</v>
       </c>
       <c r="AJ20" t="n">
-        <v>500.7</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>500.2666666666667</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>499.7625</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>499.61</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>499.15</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>499.1357142857143</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>499.14375</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>499.2611111111111</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>499.28</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>56.41551205120805</v>
+        <v>499.325</v>
       </c>
       <c r="AT20" t="n">
-        <v>49.38213802130844</v>
+        <v>499.5833333333333</v>
       </c>
       <c r="AU20" t="n">
-        <v>45.46186416932328</v>
+        <v>499.7125</v>
       </c>
       <c r="AV20" t="n">
-        <v>42.41506689845014</v>
+        <v>499.71</v>
       </c>
       <c r="AW20" t="n">
-        <v>40.39588469138904</v>
+        <v>499.3166666666667</v>
       </c>
       <c r="AX20" t="n">
-        <v>38.93221411528462</v>
+        <v>498.7857142857143</v>
       </c>
       <c r="AY20" t="n">
-        <v>38.9088432870665</v>
+        <v>499.4625</v>
       </c>
       <c r="AZ20" t="n">
-        <v>37.44230582418901</v>
+        <v>499.0333333333334</v>
       </c>
       <c r="BA20" t="n">
-        <v>35.74928810480007</v>
+        <v>500.035</v>
       </c>
       <c r="BB20" t="n">
-        <v>364</v>
+        <v>49.73448878796282</v>
       </c>
       <c r="BC20" t="n">
-        <v>364</v>
+        <v>43.41439533406197</v>
       </c>
       <c r="BD20" t="n">
-        <v>364</v>
+        <v>43.45261607486942</v>
       </c>
       <c r="BE20" t="n">
-        <v>364</v>
+        <v>44.27940717760345</v>
       </c>
       <c r="BF20" t="n">
-        <v>364</v>
+        <v>43.22691741136406</v>
       </c>
       <c r="BG20" t="n">
-        <v>364</v>
+        <v>41.33431395588999</v>
       </c>
       <c r="BH20" t="n">
-        <v>364</v>
+        <v>40.05634898177816</v>
       </c>
       <c r="BI20" t="n">
-        <v>364</v>
+        <v>38.762940491603</v>
       </c>
       <c r="BJ20" t="n">
-        <v>364</v>
+        <v>37.83521871219988</v>
       </c>
       <c r="BK20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BL20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BM20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BN20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BO20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BP20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BQ20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BR20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BS20" t="n">
-        <v>669</v>
+        <v>344</v>
       </c>
       <c r="BT20" t="n">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="BU20" t="n">
-        <v>0.9333333333333333</v>
+        <v>612</v>
       </c>
       <c r="BV20" t="n">
-        <v>0.875</v>
+        <v>612</v>
       </c>
       <c r="BW20" t="n">
-        <v>0.7352941176470589</v>
+        <v>612</v>
       </c>
       <c r="BX20" t="n">
-        <v>0.7272727272727273</v>
+        <v>612</v>
       </c>
       <c r="BY20" t="n">
-        <v>0.6538461538461539</v>
+        <v>612</v>
       </c>
       <c r="BZ20" t="n">
-        <v>0.7222222222222222</v>
+        <v>612</v>
       </c>
       <c r="CA20" t="n">
-        <v>0.6833333333333333</v>
+        <v>612</v>
       </c>
       <c r="CB20" t="n">
-        <v>0.6833333333333333</v>
+        <v>612</v>
+      </c>
+      <c r="CC20" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE20" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="CF20" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="CG20" t="n">
+        <v>0.6206896551724138</v>
+      </c>
+      <c r="CH20" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="CI20" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="CJ20" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="CK20" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="CL20" t="n">
+        <v>515.37</v>
+      </c>
+      <c r="CM20" t="n">
+        <v>25.28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S19_G7_518_22_REL1</t>
+          <t>S20_G7_521_20_REL1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C21" t="n">
-        <v>22</v>
+        <v>29.65159377316531</v>
       </c>
       <c r="D21" t="n">
-        <v>32.61675315048184</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F21" t="n">
         <v>200</v>
       </c>
       <c r="G21" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="H21" t="inlineStr">
+        <v>79</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="N21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>REL1</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>514.1230714739431</v>
-      </c>
-      <c r="J21" t="n">
-        <v>19.06573041370357</v>
-      </c>
-      <c r="K21" t="n">
-        <v>511.9821413416577</v>
-      </c>
-      <c r="L21" t="n">
-        <v>27.91827885165699</v>
-      </c>
-      <c r="M21" t="n">
-        <v>515.1548471204077</v>
-      </c>
-      <c r="N21" t="n">
-        <v>27.24487376706675</v>
-      </c>
-      <c r="O21" t="n">
-        <v>516.1466417575405</v>
-      </c>
-      <c r="P21" t="n">
-        <v>25.72373278166882</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>515.6790310948037</v>
-      </c>
       <c r="R21" t="n">
-        <v>27.85736289932167</v>
+        <v>530.75</v>
       </c>
       <c r="S21" t="n">
-        <v>513.1016423917234</v>
+        <v>4.48</v>
       </c>
       <c r="T21" t="n">
-        <v>26.98296502485333</v>
+        <v>530.12</v>
       </c>
       <c r="U21" t="n">
-        <v>513.1950255247972</v>
+        <v>4.63</v>
       </c>
       <c r="V21" t="n">
-        <v>25.61352793158968</v>
+        <v>527.76</v>
       </c>
       <c r="W21" t="n">
-        <v>514.8601869476781</v>
+        <v>5.54</v>
       </c>
       <c r="X21" t="n">
-        <v>24.35503038804468</v>
+        <v>526.39</v>
       </c>
       <c r="Y21" t="n">
-        <v>515.3720268900395</v>
+        <v>6.17</v>
       </c>
       <c r="Z21" t="n">
-        <v>25.28008917451057</v>
+        <v>526.38</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>525.11</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>14.82</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>522.91</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>19.1</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>520.4400000000001</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>20.01</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>517.95</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>21.36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>499.325</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>499.5833333333333</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>499.7125</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>499.71</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>499.3166666666667</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>498.7857142857143</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>499.4625</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>499.0333333333334</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>500.035</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>49.73448878796282</v>
+        <v>500.7</v>
       </c>
       <c r="AT21" t="n">
-        <v>43.41439533406197</v>
+        <v>500.2666666666667</v>
       </c>
       <c r="AU21" t="n">
-        <v>43.45261607486942</v>
+        <v>499.7625</v>
       </c>
       <c r="AV21" t="n">
-        <v>44.27940717760345</v>
+        <v>499.61</v>
       </c>
       <c r="AW21" t="n">
-        <v>43.22691741136406</v>
+        <v>499.15</v>
       </c>
       <c r="AX21" t="n">
-        <v>41.33431395588999</v>
+        <v>499.1357142857143</v>
       </c>
       <c r="AY21" t="n">
-        <v>40.05634898177816</v>
+        <v>499.14375</v>
       </c>
       <c r="AZ21" t="n">
-        <v>38.762940491603</v>
+        <v>499.2611111111111</v>
       </c>
       <c r="BA21" t="n">
-        <v>37.83521871219988</v>
+        <v>499.28</v>
       </c>
       <c r="BB21" t="n">
-        <v>344</v>
+        <v>56.41551205120805</v>
       </c>
       <c r="BC21" t="n">
-        <v>344</v>
+        <v>49.38213802130844</v>
       </c>
       <c r="BD21" t="n">
-        <v>344</v>
+        <v>45.46186416932328</v>
       </c>
       <c r="BE21" t="n">
-        <v>344</v>
+        <v>42.41506689845014</v>
       </c>
       <c r="BF21" t="n">
-        <v>344</v>
+        <v>40.39588469138904</v>
       </c>
       <c r="BG21" t="n">
-        <v>344</v>
+        <v>38.93221411528462</v>
       </c>
       <c r="BH21" t="n">
-        <v>344</v>
+        <v>38.9088432870665</v>
       </c>
       <c r="BI21" t="n">
-        <v>344</v>
+        <v>37.44230582418901</v>
       </c>
       <c r="BJ21" t="n">
-        <v>344</v>
+        <v>35.74928810480007</v>
       </c>
       <c r="BK21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BL21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BM21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BN21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BO21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BP21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BQ21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BR21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BS21" t="n">
-        <v>612</v>
+        <v>364</v>
       </c>
       <c r="BT21" t="n">
-        <v>0.5333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BU21" t="n">
-        <v>0</v>
+        <v>669</v>
       </c>
       <c r="BV21" t="n">
-        <v>0.4642857142857143</v>
+        <v>669</v>
       </c>
       <c r="BW21" t="n">
-        <v>0.5357142857142857</v>
+        <v>669</v>
       </c>
       <c r="BX21" t="n">
-        <v>0.6206896551724138</v>
+        <v>669</v>
       </c>
       <c r="BY21" t="n">
-        <v>0.4333333333333333</v>
+        <v>669</v>
       </c>
       <c r="BZ21" t="n">
-        <v>0.5333333333333333</v>
+        <v>669</v>
       </c>
       <c r="CA21" t="n">
-        <v>0.5666666666666667</v>
+        <v>669</v>
       </c>
       <c r="CB21" t="n">
-        <v>0.7333333333333333</v>
+        <v>669</v>
+      </c>
+      <c r="CC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD21" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="CE21" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CF21" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="CG21" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="CH21" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="CI21" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="CJ21" t="n">
+        <v>0.6833333333333333</v>
+      </c>
+      <c r="CK21" t="n">
+        <v>0.6833333333333333</v>
+      </c>
+      <c r="CL21" t="n">
+        <v>517.95</v>
+      </c>
+      <c r="CM21" t="n">
+        <v>21.36</v>
       </c>
     </row>
     <row r="22">
@@ -5760,10 +6475,10 @@
         <v>519.75</v>
       </c>
       <c r="C22" t="n">
+        <v>29.50333580429949</v>
+      </c>
+      <c r="D22" t="n">
         <v>19.9</v>
-      </c>
-      <c r="D22" t="n">
-        <v>29.50333580429949</v>
       </c>
       <c r="E22" t="n">
         <v>519.75</v>
@@ -5772,224 +6487,239 @@
         <v>200</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3605</v>
-      </c>
-      <c r="H22" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3315</v>
+      </c>
       <c r="I22" t="n">
-        <v>522.9297776956653</v>
+        <v>2.3005</v>
       </c>
       <c r="J22" t="n">
-        <v>15.62223815127209</v>
+        <v>2.282</v>
       </c>
       <c r="K22" t="n">
-        <v>521.098360285991</v>
+        <v>2.27</v>
       </c>
       <c r="L22" t="n">
-        <v>19.8504707431926</v>
+        <v>2.2665</v>
       </c>
       <c r="M22" t="n">
-        <v>519.6407574563937</v>
+        <v>2.2495</v>
       </c>
       <c r="N22" t="n">
-        <v>21.44677544091044</v>
+        <v>2.387</v>
       </c>
       <c r="O22" t="n">
-        <v>519.8388490541672</v>
+        <v>2.304</v>
       </c>
       <c r="P22" t="n">
-        <v>20.94279435840264</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>520.175698053347</v>
-      </c>
+        <v>2.331</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="n">
-        <v>21.25277643840866</v>
+        <v>522.9285000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>519.3372183166171</v>
+        <v>15.622</v>
       </c>
       <c r="T22" t="n">
-        <v>21.4557071650195</v>
+        <v>521.099</v>
       </c>
       <c r="U22" t="n">
-        <v>518.6777538012961</v>
+        <v>19.8505</v>
       </c>
       <c r="V22" t="n">
-        <v>22.18974692237893</v>
+        <v>519.6405000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>518.4829846001683</v>
+        <v>21.4475</v>
       </c>
       <c r="X22" t="n">
-        <v>22.1099743360378</v>
+        <v>519.8394999999999</v>
       </c>
       <c r="Y22" t="n">
-        <v>518.0922925771032</v>
+        <v>20.942</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4463604565126</v>
+        <v>520.1750000000001</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>21.25350000000001</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>519.3355</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>21.4545</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>518.679</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>22.189</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>518.4835</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>22.11</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>518.0920000000001</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>22.447</v>
       </c>
       <c r="AJ22" t="n">
-        <v>498.9400000000001</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>499.0266666666666</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>498.99125</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>498.9405</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>499.0275</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>498.9909999999999</v>
+      </c>
+      <c r="AV22" t="n">
         <v>498.9640000000001</v>
       </c>
-      <c r="AN22" t="n">
-        <v>498.9695833333333</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>498.9157142857142</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>498.974375</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>498.9616666666667</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>499.01625</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>54.42330811610101</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>49.16873487851948</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>46.96878448697278</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>44.97684797339992</v>
-      </c>
       <c r="AW22" t="n">
-        <v>43.30793575184325</v>
+        <v>498.9689999999999</v>
       </c>
       <c r="AX22" t="n">
-        <v>42.00886802381409</v>
+        <v>498.9175</v>
       </c>
       <c r="AY22" t="n">
-        <v>41.02436366479292</v>
+        <v>498.9729999999998</v>
       </c>
       <c r="AZ22" t="n">
-        <v>40.0610127198759</v>
+        <v>498.9615</v>
       </c>
       <c r="BA22" t="n">
-        <v>39.16650868803363</v>
+        <v>499.016</v>
       </c>
       <c r="BB22" t="n">
+        <v>54.424</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>49.1675</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>46.9685</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>44.9765</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>43.308</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>42.0095</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>41.02500000000001</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>40.061</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>39.1665</v>
+      </c>
+      <c r="BK22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BC22" t="n">
+      <c r="BL22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BD22" t="n">
+      <c r="BM22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BE22" t="n">
+      <c r="BN22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BF22" t="n">
+      <c r="BO22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BG22" t="n">
+      <c r="BP22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BH22" t="n">
+      <c r="BQ22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BI22" t="n">
+      <c r="BR22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BJ22" t="n">
+      <c r="BS22" t="n">
         <v>357.05</v>
       </c>
-      <c r="BK22" t="n">
+      <c r="BT22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BL22" t="n">
+      <c r="BU22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BM22" t="n">
+      <c r="BV22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BN22" t="n">
+      <c r="BW22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BO22" t="n">
+      <c r="BX22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BP22" t="n">
+      <c r="BY22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BQ22" t="n">
+      <c r="BZ22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BR22" t="n">
+      <c r="CA22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BS22" t="n">
+      <c r="CB22" t="n">
         <v>643.15</v>
       </c>
-      <c r="BT22" t="n">
-        <v>0.6937031024531024</v>
-      </c>
-      <c r="BU22" t="n">
-        <v>0.690429292929293</v>
-      </c>
-      <c r="BV22" t="n">
-        <v>0.7274813623301812</v>
-      </c>
-      <c r="BW22" t="n">
-        <v>0.7675414557393123</v>
-      </c>
-      <c r="BX22" t="n">
-        <v>0.7416574863697722</v>
-      </c>
-      <c r="BY22" t="n">
-        <v>0.79891167747901</v>
-      </c>
-      <c r="BZ22" t="n">
-        <v>0.797496802253013</v>
-      </c>
-      <c r="CA22" t="n">
-        <v>0.7393032211412598</v>
-      </c>
-      <c r="CB22" t="n">
-        <v>0.8131740936106739</v>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="n">
+        <v>518.0920000000001</v>
+      </c>
+      <c r="CM22" t="n">
+        <v>22.447</v>
       </c>
     </row>
     <row r="23">
@@ -6002,10 +6732,10 @@
         <v>1.446411166701189</v>
       </c>
       <c r="C23" t="n">
+        <v>2.251014542672344</v>
+      </c>
+      <c r="D23" t="n">
         <v>1.518309309032496</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2.251014542672343</v>
       </c>
       <c r="E23" t="n">
         <v>1.446411166701189</v>
@@ -6014,224 +6744,239 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02896913057576616</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>1.547493729262017</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3071820135907769</v>
+      </c>
       <c r="I23" t="n">
-        <v>8.252793289428837</v>
+        <v>0.309234623921027</v>
       </c>
       <c r="J23" t="n">
-        <v>9.184731913574772</v>
+        <v>0.3040013850383961</v>
       </c>
       <c r="K23" t="n">
-        <v>6.797690092994054</v>
+        <v>0.2829171349762292</v>
       </c>
       <c r="L23" t="n">
-        <v>7.245568840567812</v>
+        <v>0.2671344033884146</v>
       </c>
       <c r="M23" t="n">
-        <v>6.742726377718101</v>
+        <v>0.2454528575167906</v>
       </c>
       <c r="N23" t="n">
-        <v>5.744326683178498</v>
+        <v>0.221694431713184</v>
       </c>
       <c r="O23" t="n">
-        <v>6.003120277910797</v>
+        <v>0.2621249199984819</v>
       </c>
       <c r="P23" t="n">
-        <v>5.73246427578042</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>4.431736225609862</v>
-      </c>
+        <v>0.2829710790503994</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="n">
-        <v>5.255777510573062</v>
+        <v>8.2529090724359</v>
       </c>
       <c r="S23" t="n">
-        <v>5.010546295152607</v>
+        <v>9.185310125698704</v>
       </c>
       <c r="T23" t="n">
-        <v>3.52284432836681</v>
+        <v>6.796770827695336</v>
       </c>
       <c r="U23" t="n">
-        <v>4.661298737672322</v>
+        <v>7.245573948425705</v>
       </c>
       <c r="V23" t="n">
-        <v>3.042796076115345</v>
+        <v>6.741663448484469</v>
       </c>
       <c r="W23" t="n">
-        <v>4.012203311586754</v>
+        <v>5.743803869800643</v>
       </c>
       <c r="X23" t="n">
-        <v>3.11742881603407</v>
+        <v>6.003096985810957</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.413195232036458</v>
+        <v>5.733021248136008</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.307894292028126</v>
+        <v>4.431018060517407</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>5.255295349504756</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>5.009831886033283</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.522033615608131</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>4.660713634085164</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>3.043009071712786</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>4.012008651667222</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>3.117942979121432</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3.412976166894444</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>3.307591109458426</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.668252846706237</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.673294395306402</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.400630742227207</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.668191114518377</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>2.672930335595629</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.401337127518756</v>
+      </c>
+      <c r="AV23" t="n">
         <v>2.116999863262303</v>
       </c>
-      <c r="AN23" t="n">
-        <v>1.901019799802131</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1.781109250191327</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.48011754400756</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.390640883289722</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.289343850875123</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.450802257657946</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>4.218458381044331</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>3.726799203959891</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.698256541964235</v>
-      </c>
       <c r="AW23" t="n">
-        <v>4.021849527661769</v>
+        <v>1.901007765979874</v>
       </c>
       <c r="AX23" t="n">
-        <v>3.939470487710157</v>
+        <v>1.781028310304266</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.578586711820595</v>
+        <v>1.48155359424881</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.40912813286522</v>
+        <v>1.390067302422142</v>
       </c>
       <c r="BA23" t="n">
-        <v>3.180912801827158</v>
+        <v>1.290603286105098</v>
       </c>
       <c r="BB23" t="n">
+        <v>4.452494747182102</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.218752465886218</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.727693339262089</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>3.69822329319307</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>4.022130359844015</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>3.940207682210085</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>3.578475859033313</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>3.408500055974614</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>3.18017754386863</v>
+      </c>
+      <c r="BK23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BC23" t="n">
+      <c r="BL23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BD23" t="n">
+      <c r="BM23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BE23" t="n">
+      <c r="BN23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BF23" t="n">
+      <c r="BO23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BG23" t="n">
+      <c r="BP23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BH23" t="n">
+      <c r="BQ23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BI23" t="n">
+      <c r="BR23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BJ23" t="n">
+      <c r="BS23" t="n">
         <v>27.06225765662732</v>
       </c>
-      <c r="BK23" t="n">
+      <c r="BT23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BL23" t="n">
+      <c r="BU23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BM23" t="n">
+      <c r="BV23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BN23" t="n">
+      <c r="BW23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BO23" t="n">
+      <c r="BX23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BP23" t="n">
+      <c r="BY23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BQ23" t="n">
+      <c r="BZ23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BR23" t="n">
+      <c r="CA23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BS23" t="n">
+      <c r="CB23" t="n">
         <v>33.09996819842645</v>
       </c>
-      <c r="BT23" t="n">
-        <v>0.3135632059996465</v>
-      </c>
-      <c r="BU23" t="n">
-        <v>0.3185828084379738</v>
-      </c>
-      <c r="BV23" t="n">
-        <v>0.2073727312660466</v>
-      </c>
-      <c r="BW23" t="n">
-        <v>0.1200172589551909</v>
-      </c>
-      <c r="BX23" t="n">
-        <v>0.2806849677381867</v>
-      </c>
-      <c r="BY23" t="n">
-        <v>0.1454297387434406</v>
-      </c>
-      <c r="BZ23" t="n">
-        <v>0.1504302562552425</v>
-      </c>
-      <c r="CA23" t="n">
-        <v>0.2751449858059022</v>
-      </c>
-      <c r="CB23" t="n">
-        <v>0.1220955110383746</v>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="n">
+        <v>3.412976166894444</v>
+      </c>
+      <c r="CM23" t="n">
+        <v>3.307591109458426</v>
       </c>
     </row>
   </sheetData>
